--- a/Config/BossEntryConfig.xlsx
+++ b/Config/BossEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15690" windowHeight="14160"/>
+    <workbookView windowWidth="16275" windowHeight="15945"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>EntryId</t>
+    <t>Desc</t>
   </si>
   <si>
     <t>##</t>
@@ -58,7 +58,7 @@
     <t>名字</t>
   </si>
   <si>
-    <t>机制id</t>
+    <t>描述</t>
   </si>
   <si>
     <t>禁搓红心</t>
@@ -1102,7 +1102,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4">

--- a/Config/BossEntryConfig.xlsx
+++ b/Config/BossEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16275" windowHeight="15945"/>
+    <workbookView windowWidth="13620" windowHeight="13155"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -43,6 +43,12 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
     <t>Desc</t>
   </si>
   <si>
@@ -55,46 +61,136 @@
     <t>string</t>
   </si>
   <si>
+    <t>BossEntryType</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>名字</t>
   </si>
   <si>
+    <t>机制类型</t>
+  </si>
+  <si>
+    <t>值</t>
+  </si>
+  <si>
     <t>描述</t>
   </si>
   <si>
     <t>禁搓红心</t>
   </si>
   <si>
+    <t>DisableHeart</t>
+  </si>
+  <si>
+    <t>本局搓牌时,无法出现红心花色</t>
+  </si>
+  <si>
     <t>禁搓黑桃</t>
   </si>
   <si>
+    <t>DisableSpade</t>
+  </si>
+  <si>
+    <t>本局搓牌时,无法出现黑桃花色</t>
+  </si>
+  <si>
     <t>禁搓方片</t>
   </si>
   <si>
+    <t>DisableDiamond</t>
+  </si>
+  <si>
+    <t>本局搓牌时,无法出现方片花色</t>
+  </si>
+  <si>
     <t>禁搓梅花</t>
   </si>
   <si>
+    <t>DisablePlumBlossom</t>
+  </si>
+  <si>
+    <t>本局搓牌时,无法出现梅花花色</t>
+  </si>
+  <si>
     <t>禁搓人头</t>
   </si>
   <si>
+    <t>DisableHead</t>
+  </si>
+  <si>
+    <t>本局搓牌时,无法出现人头牌</t>
+  </si>
+  <si>
     <t>燧石</t>
   </si>
   <si>
+    <t>Flint</t>
+  </si>
+  <si>
+    <t>-0.5</t>
+  </si>
+  <si>
+    <t>本局结算时,牌型的倍率减半</t>
+  </si>
+  <si>
     <t>锋芒</t>
   </si>
   <si>
+    <t>Edge</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>本局内你的随机一种遗物将失效</t>
+  </si>
+  <si>
     <t>孤注一掷</t>
   </si>
   <si>
-    <t>偷天换日</t>
+    <t>AllIn</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>领主每次都会投注你当前血量一半筹码</t>
   </si>
   <si>
     <t>同花</t>
   </si>
   <si>
+    <t>FlushDamage</t>
+  </si>
+  <si>
+    <t>-0.4</t>
+  </si>
+  <si>
+    <t>同花牌型在攻击时,伤害降低40%</t>
+  </si>
+  <si>
     <t>同花顺</t>
   </si>
   <si>
+    <t>FlushStraightDamage</t>
+  </si>
+  <si>
+    <t>-0.25</t>
+  </si>
+  <si>
+    <t>同花顺牌型在攻击时,伤害降低25%</t>
+  </si>
+  <si>
     <t>顺子</t>
+  </si>
+  <si>
+    <t>StraightDamage</t>
+  </si>
+  <si>
+    <t>顺子牌型在攻击时,伤害降低50%</t>
   </si>
 </sst>
 </file>
@@ -1068,16 +1164,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="3.8" style="1" customWidth="1"/>
     <col min="3" max="3" width="8.36666666666667" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="20.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.73333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.2166666666667" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1090,138 +1189,228 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:4">
+    <row r="5" customFormat="1" spans="1:6">
       <c r="A5" s="1"/>
       <c r="B5" s="2">
         <v>101</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:6">
       <c r="B6" s="2">
         <v>102</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6"/>
+      <c r="F6" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:6">
       <c r="B7" s="2">
         <v>103</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7"/>
+      <c r="F7" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6">
       <c r="B8" s="2">
         <v>104</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8"/>
+      <c r="F8" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6">
       <c r="B9" s="2">
         <v>105</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9"/>
+      <c r="F9" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:6">
       <c r="B10" s="2">
         <v>106</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:6">
       <c r="B11" s="2">
         <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>34</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:6">
       <c r="B12" s="2">
         <v>108</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:6">
       <c r="B13" s="2">
         <v>109</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>42</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:6">
       <c r="B14" s="2">
         <v>110</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>17</v>
+        <v>46</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:6">
       <c r="B15" s="2">
         <v>111</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="B16" s="2">
-        <v>112</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="2">
-        <v>113</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>20</v>
+        <v>50</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Config/BossEntryConfig.xlsx
+++ b/Config/BossEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="13620" windowHeight="13155"/>
+    <workbookView windowWidth="14415" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="97">
   <si>
     <t>##var</t>
   </si>
@@ -64,7 +64,7 @@
     <t>BossEntryType</t>
   </si>
   <si>
-    <t>float</t>
+    <t>float[]</t>
   </si>
   <si>
     <t>名字</t>
@@ -85,7 +85,7 @@
     <t>DisableHeart</t>
   </si>
   <si>
-    <t>本局搓牌时,无法出现红心花色</t>
+    <t>本关内搓牌时,无法出现红心花色</t>
   </si>
   <si>
     <t>禁搓黑桃</t>
@@ -94,7 +94,7 @@
     <t>DisableSpade</t>
   </si>
   <si>
-    <t>本局搓牌时,无法出现黑桃花色</t>
+    <t>本关内搓牌时,无法出现黑桃花色</t>
   </si>
   <si>
     <t>禁搓方片</t>
@@ -103,7 +103,7 @@
     <t>DisableDiamond</t>
   </si>
   <si>
-    <t>本局搓牌时,无法出现方片花色</t>
+    <t>本关内搓牌时,无法出现方片花色</t>
   </si>
   <si>
     <t>禁搓梅花</t>
@@ -112,7 +112,7 @@
     <t>DisablePlumBlossom</t>
   </si>
   <si>
-    <t>本局搓牌时,无法出现梅花花色</t>
+    <t>本关内搓牌时,无法出现梅花花色</t>
   </si>
   <si>
     <t>禁搓人头</t>
@@ -121,7 +121,7 @@
     <t>DisableHead</t>
   </si>
   <si>
-    <t>本局搓牌时,无法出现人头牌</t>
+    <t>本关内搓牌时,无法出现人头牌</t>
   </si>
   <si>
     <t>燧石</t>
@@ -130,34 +130,7 @@
     <t>Flint</t>
   </si>
   <si>
-    <t>-0.5</t>
-  </si>
-  <si>
-    <t>本局结算时,牌型的倍率减半</t>
-  </si>
-  <si>
-    <t>锋芒</t>
-  </si>
-  <si>
-    <t>Edge</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>本局内你的随机一种遗物将失效</t>
-  </si>
-  <si>
-    <t>孤注一掷</t>
-  </si>
-  <si>
-    <t>AllIn</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>领主每次都会投注你当前血量一半筹码</t>
+    <t>本关内结算时,牌型的倍率减半</t>
   </si>
   <si>
     <t>同花</t>
@@ -166,10 +139,7 @@
     <t>FlushDamage</t>
   </si>
   <si>
-    <t>-0.4</t>
-  </si>
-  <si>
-    <t>同花牌型在攻击时,伤害降低40%</t>
+    <t>本关内同花牌型在攻击时,伤害降低40%</t>
   </si>
   <si>
     <t>同花顺</t>
@@ -178,10 +148,7 @@
     <t>FlushStraightDamage</t>
   </si>
   <si>
-    <t>-0.25</t>
-  </si>
-  <si>
-    <t>同花顺牌型在攻击时,伤害降低25%</t>
+    <t>本关内同花顺牌型在攻击时,伤害降低25%</t>
   </si>
   <si>
     <t>顺子</t>
@@ -190,7 +157,172 @@
     <t>StraightDamage</t>
   </si>
   <si>
-    <t>顺子牌型在攻击时,伤害降低50%</t>
+    <t>本关内顺子牌型在攻击时,伤害降低50%</t>
+  </si>
+  <si>
+    <t>诅咒之躯</t>
+  </si>
+  <si>
+    <t>CurseBody</t>
+  </si>
+  <si>
+    <t>0.2|-0.05</t>
+  </si>
+  <si>
+    <t>玩家在本关内受到的伤害+20%,且每次攻击怪物时,同时会使当前自身的血量降低5%</t>
+  </si>
+  <si>
+    <t>攻击钝化</t>
+  </si>
+  <si>
+    <t>PlayerDamageDown</t>
+  </si>
+  <si>
+    <t>玩家在本关内造成的伤害-50%</t>
+  </si>
+  <si>
+    <t>失效光环</t>
+  </si>
+  <si>
+    <t>SkillDisable</t>
+  </si>
+  <si>
+    <t>玩家在本关内无法使用任何技能</t>
+  </si>
+  <si>
+    <t>手牌烙印</t>
+  </si>
+  <si>
+    <t>HandBrand</t>
+  </si>
+  <si>
+    <t>玩家在本关内亮出的手牌中将随机有1张不参与牌型构成</t>
+  </si>
+  <si>
+    <t>灵活身姿</t>
+  </si>
+  <si>
+    <t>MonsterEvade</t>
+  </si>
+  <si>
+    <t>0.6|1</t>
+  </si>
+  <si>
+    <t>本关内所有敌人都拥有60%闪避率,且成功闪避时会对玩家造成1次自身攻击力的伤害</t>
+  </si>
+  <si>
+    <t>双倍痛击</t>
+  </si>
+  <si>
+    <t>MonsterDamageUp</t>
+  </si>
+  <si>
+    <t>本关内所有敌人造成的伤害+100%</t>
+  </si>
+  <si>
+    <t>收藏禁用</t>
+  </si>
+  <si>
+    <t>RelicDisable</t>
+  </si>
+  <si>
+    <t>本关内每回合将随机失效2件玩家所持有的收藏品效果</t>
+  </si>
+  <si>
+    <t>经济黑洞</t>
+  </si>
+  <si>
+    <t>GoldThorn</t>
+  </si>
+  <si>
+    <t>本关内敌人造成的伤害将附加玩家截止到目前为止所消耗的金币数10%的额外伤害</t>
+  </si>
+  <si>
+    <t>脆弱身躯</t>
+  </si>
+  <si>
+    <t>FragileBody</t>
+  </si>
+  <si>
+    <t>-0.5|1</t>
+  </si>
+  <si>
+    <t>本关内玩家的生命值上限-50%,且无法通过任何手段恢复生命值</t>
+  </si>
+  <si>
+    <t>手牌压缩</t>
+  </si>
+  <si>
+    <t>HandCompress</t>
+  </si>
+  <si>
+    <t>本关内玩家每回合的手牌数量从5张降低至4张</t>
+  </si>
+  <si>
+    <t>狂暴增长</t>
+  </si>
+  <si>
+    <t>BossRage</t>
+  </si>
+  <si>
+    <t>0.2|0.5</t>
+  </si>
+  <si>
+    <t>本关内BOSS每损失20%生命值,其攻击力+50%</t>
+  </si>
+  <si>
+    <t>黑暗护盾</t>
+  </si>
+  <si>
+    <t>BossShield</t>
+  </si>
+  <si>
+    <t>本关内BOSS会免疫前4次受到的所有伤害</t>
+  </si>
+  <si>
+    <t>回合制约</t>
+  </si>
+  <si>
+    <t>RoundLimit</t>
+  </si>
+  <si>
+    <t>本关内将限制回合数为5,若玩家5回合内未击杀BOSS,将直接失去所有生命值,立即死亡</t>
+  </si>
+  <si>
+    <t>窃取指环</t>
+  </si>
+  <si>
+    <t>AttackSteal</t>
+  </si>
+  <si>
+    <t>本关内每回合开始时,boss会偷取玩家当前10%的攻击力</t>
+  </si>
+  <si>
+    <t>胆小首领</t>
+  </si>
+  <si>
+    <t>BossTimid</t>
+  </si>
+  <si>
+    <t>本关内在非BOSS敌人死亡前,BOSS将免疫受到的所有伤害</t>
+  </si>
+  <si>
+    <t>方片红桃</t>
+  </si>
+  <si>
+    <t>DisableRedSuit</t>
+  </si>
+  <si>
+    <t>本关内玩家手上的方片和红桃牌将失效[无法凑成牌型、无法提供攻击力]</t>
+  </si>
+  <si>
+    <t>黑桃梅花</t>
+  </si>
+  <si>
+    <t>DisableBlackSuit</t>
+  </si>
+  <si>
+    <t>本关内玩家手上的黑桃和梅花牌将失效[无法凑成牌型、无法提供攻击力]</t>
   </si>
 </sst>
 </file>
@@ -661,158 +793,159 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1164,16 +1297,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
     <col min="2" max="2" width="3.8" style="1" customWidth="1"/>
     <col min="3" max="3" width="8.36666666666667" style="2" customWidth="1"/>
     <col min="4" max="4" width="20.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.73333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" customWidth="1"/>
     <col min="6" max="6" width="25.2166666666667" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="7" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1183,7 +1316,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1203,7 +1336,7 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -1223,7 +1356,7 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1236,181 +1369,446 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:6">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2">
+    <row r="5" spans="1:6">
+      <c r="B5" s="3">
         <v>101</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>15</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>102</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E6"/>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
       <c r="F6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>103</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>21</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E7"/>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
       <c r="F7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>104</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E8"/>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
       <c r="F8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="B9" s="2">
+      <c r="B9" s="3">
         <v>105</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E9"/>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
       <c r="F9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="B10" s="2">
+      <c r="B10" s="3">
         <v>106</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="1">
+        <v>-0.5</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="1" t="s">
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" s="3">
+        <v>107</v>
+      </c>
+      <c r="C11" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="B11" s="2">
-        <v>107</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1">
+        <v>-0.4</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="1" t="s">
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" s="3">
+        <v>108</v>
+      </c>
+      <c r="C12" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="B12" s="2">
-        <v>108</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="E12" s="1">
+        <v>-0.25</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="1" t="s">
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" s="3">
+        <v>109</v>
+      </c>
+      <c r="C13" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="E13" s="1">
+        <v>-0.5</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="B13" s="2">
-        <v>109</v>
-      </c>
-      <c r="C13" s="2" t="s">
+    <row r="14" spans="1:6">
+      <c r="B14" s="3">
+        <v>110</v>
+      </c>
+      <c r="C14" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="B14" s="2">
-        <v>110</v>
-      </c>
-      <c r="C14" s="2" t="s">
+    <row r="15" spans="1:6">
+      <c r="B15" s="3">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D15" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E15" s="3">
+        <v>-0.5</v>
+      </c>
+      <c r="F15" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="1" t="s">
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" s="3">
+        <v>112</v>
+      </c>
+      <c r="C16" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="B15" s="2">
-        <v>111</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D16" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E16" s="3">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="1" t="s">
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="3">
+        <v>113</v>
+      </c>
+      <c r="C17" t="s">
         <v>52</v>
+      </c>
+      <c r="D17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="3">
+        <v>114</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="3">
+        <v>115</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="3">
+        <v>116</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2</v>
+      </c>
+      <c r="F20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="3">
+        <v>117</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="3">
+        <v>118</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="3">
+        <v>119</v>
+      </c>
+      <c r="C23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4</v>
+      </c>
+      <c r="F23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="3">
+        <v>120</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="3">
+        <v>121</v>
+      </c>
+      <c r="C25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="3">
+        <v>4</v>
+      </c>
+      <c r="F25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="3">
+        <v>122</v>
+      </c>
+      <c r="C26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="3">
+        <v>5</v>
+      </c>
+      <c r="F26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="3">
+        <v>123</v>
+      </c>
+      <c r="C27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="3">
+        <v>124</v>
+      </c>
+      <c r="C28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" s="3">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="3">
+        <v>125</v>
+      </c>
+      <c r="C29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" s="3">
+        <v>1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="3">
+        <v>126</v>
+      </c>
+      <c r="C30" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Config/BossEntryConfig.xlsx
+++ b/Config/BossEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14415" windowHeight="11400"/>
+    <workbookView windowWidth="13695" windowHeight="11505"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="143">
   <si>
     <t>##var</t>
   </si>
@@ -124,40 +124,43 @@
     <t>本关内搓牌时,无法出现人头牌</t>
   </si>
   <si>
-    <t>燧石</t>
-  </si>
-  <si>
-    <t>Flint</t>
-  </si>
-  <si>
-    <t>本关内结算时,牌型的倍率减半</t>
-  </si>
-  <si>
-    <t>同花</t>
+    <t>钝化之躯</t>
+  </si>
+  <si>
+    <t>PlayerDamageDown</t>
+  </si>
+  <si>
+    <t>本关内玩家造成的伤害-50%</t>
+  </si>
+  <si>
+    <t>禁用同花</t>
   </si>
   <si>
     <t>FlushDamage</t>
   </si>
   <si>
-    <t>本关内同花牌型在攻击时,伤害降低40%</t>
-  </si>
-  <si>
-    <t>同花顺</t>
-  </si>
-  <si>
-    <t>FlushStraightDamage</t>
-  </si>
-  <si>
-    <t>本关内同花顺牌型在攻击时,伤害降低25%</t>
-  </si>
-  <si>
-    <t>顺子</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>本关内亮出同花牌型时,将无法造成伤害</t>
+  </si>
+  <si>
+    <t>禁用对子</t>
+  </si>
+  <si>
+    <t>CoupletDamage</t>
+  </si>
+  <si>
+    <t>本关内亮出对子牌型时,将无法造成伤害</t>
+  </si>
+  <si>
+    <t>禁用顺子</t>
   </si>
   <si>
     <t>StraightDamage</t>
   </si>
   <si>
-    <t>本关内顺子牌型在攻击时,伤害降低50%</t>
+    <t>本关内亮出顺子牌型时,将无法造成伤害</t>
   </si>
   <si>
     <t>诅咒之躯</t>
@@ -166,19 +169,7 @@
     <t>CurseBody</t>
   </si>
   <si>
-    <t>0.2|-0.05</t>
-  </si>
-  <si>
-    <t>玩家在本关内受到的伤害+20%,且每次攻击怪物时,同时会使当前自身的血量降低5%</t>
-  </si>
-  <si>
-    <t>攻击钝化</t>
-  </si>
-  <si>
-    <t>PlayerDamageDown</t>
-  </si>
-  <si>
-    <t>玩家在本关内造成的伤害-50%</t>
+    <t>本关内玩家每次攻击敌人时,会使自身的血量扣除10%</t>
   </si>
   <si>
     <t>失效光环</t>
@@ -187,7 +178,7 @@
     <t>SkillDisable</t>
   </si>
   <si>
-    <t>玩家在本关内无法使用任何技能</t>
+    <t>本关内无法使用任何技能[搓牌/透视/替换]</t>
   </si>
   <si>
     <t>手牌烙印</t>
@@ -196,7 +187,7 @@
     <t>HandBrand</t>
   </si>
   <si>
-    <t>玩家在本关内亮出的手牌中将随机有1张不参与牌型构成</t>
+    <t>本关内玩家亮出的手牌中将有1张不参与牌型构成</t>
   </si>
   <si>
     <t>灵活身姿</t>
@@ -205,10 +196,10 @@
     <t>MonsterEvade</t>
   </si>
   <si>
-    <t>0.6|1</t>
-  </si>
-  <si>
-    <t>本关内所有敌人都拥有60%闪避率,且成功闪避时会对玩家造成1次自身攻击力的伤害</t>
+    <t>0.6|0.1</t>
+  </si>
+  <si>
+    <t>本关内所有敌人拥有60%闪避率,且每次成功闪避时都会使自身攻击力+10%</t>
   </si>
   <si>
     <t>双倍痛击</t>
@@ -220,13 +211,13 @@
     <t>本关内所有敌人造成的伤害+100%</t>
   </si>
   <si>
-    <t>收藏禁用</t>
+    <t>禁用遗物</t>
   </si>
   <si>
     <t>RelicDisable</t>
   </si>
   <si>
-    <t>本关内每回合将随机失效2件玩家所持有的收藏品效果</t>
+    <t>本关内将随机失效3件玩家所拥有的遗物效果</t>
   </si>
   <si>
     <t>经济黑洞</t>
@@ -235,7 +226,10 @@
     <t>GoldThorn</t>
   </si>
   <si>
-    <t>本关内敌人造成的伤害将附加玩家截止到目前为止所消耗的金币数10%的额外伤害</t>
+    <t>0.3|-0.5</t>
+  </si>
+  <si>
+    <t>本关内敌人造成的伤害+30%,且每回合开始时都会失去当前50%的金币</t>
   </si>
   <si>
     <t>脆弱身躯</t>
@@ -244,10 +238,7 @@
     <t>FragileBody</t>
   </si>
   <si>
-    <t>-0.5|1</t>
-  </si>
-  <si>
-    <t>本关内玩家的生命值上限-50%,且无法通过任何手段恢复生命值</t>
+    <t>本关内玩家承受的伤害+50%,且无法通过任何手段恢复生命值</t>
   </si>
   <si>
     <t>手牌压缩</t>
@@ -262,22 +253,22 @@
     <t>狂暴增长</t>
   </si>
   <si>
-    <t>BossRage</t>
+    <t>MonsterRage</t>
   </si>
   <si>
     <t>0.2|0.5</t>
   </si>
   <si>
-    <t>本关内BOSS每损失20%生命值,其攻击力+50%</t>
+    <t>本关内敌人每损失20%生命值,其攻击力+50%</t>
   </si>
   <si>
     <t>黑暗护盾</t>
   </si>
   <si>
-    <t>BossShield</t>
-  </si>
-  <si>
-    <t>本关内BOSS会免疫前4次受到的所有伤害</t>
+    <t>MonsterShield</t>
+  </si>
+  <si>
+    <t>本关内BOSS会免疫前2次受到的所有伤害</t>
   </si>
   <si>
     <t>回合制约</t>
@@ -286,7 +277,7 @@
     <t>RoundLimit</t>
   </si>
   <si>
-    <t>本关内将限制回合数为5,若玩家5回合内未击杀BOSS,将直接失去所有生命值,立即死亡</t>
+    <t>本关内将限制回合数为5,若5回合内未击杀所有敌人,将立即死亡</t>
   </si>
   <si>
     <t>窃取指环</t>
@@ -295,7 +286,7 @@
     <t>AttackSteal</t>
   </si>
   <si>
-    <t>本关内每回合开始时,boss会偷取玩家当前10%的攻击力</t>
+    <t>本关内每回合开始时,随机1名敌人会偷取玩家当前10%的攻击力</t>
   </si>
   <si>
     <t>胆小首领</t>
@@ -323,6 +314,153 @@
   </si>
   <si>
     <t>本关内玩家手上的黑桃和梅花牌将失效[无法凑成牌型、无法提供攻击力]</t>
+  </si>
+  <si>
+    <t>禁搓偶数</t>
+  </si>
+  <si>
+    <t>DisableEven</t>
+  </si>
+  <si>
+    <t>本关内搓牌时,无法出现偶数点数的牌</t>
+  </si>
+  <si>
+    <t>禁搓A</t>
+  </si>
+  <si>
+    <t>DisableAce</t>
+  </si>
+  <si>
+    <t>本关内搓牌时,无法出现A</t>
+  </si>
+  <si>
+    <t>王权旁落</t>
+  </si>
+  <si>
+    <t>FaceDevalue</t>
+  </si>
+  <si>
+    <t>本关内人头牌[J/Q/K]伤害点数按5计算,比牌大小不变</t>
+  </si>
+  <si>
+    <t>折翼之A</t>
+  </si>
+  <si>
+    <t>AceDown</t>
+  </si>
+  <si>
+    <t>本关内A的伤害点数由11降为1,比牌大小不变</t>
+  </si>
+  <si>
+    <t>生锈拇指</t>
+  </si>
+  <si>
+    <t>RubDown</t>
+  </si>
+  <si>
+    <t>本关内搓牌次数减少1次</t>
+  </si>
+  <si>
+    <t>宿命之手</t>
+  </si>
+  <si>
+    <t>SwapLock</t>
+  </si>
+  <si>
+    <t>本关内无法使用换牌技能</t>
+  </si>
+  <si>
+    <t>有偿服务</t>
+  </si>
+  <si>
+    <t>RubFee</t>
+  </si>
+  <si>
+    <t>本关内每次搓牌需要消耗50金币,金币不足时无法搓牌</t>
+  </si>
+  <si>
+    <t>巫术灵体</t>
+  </si>
+  <si>
+    <t>MonsterRegen</t>
+  </si>
+  <si>
+    <t>本关内所有敌人每回合开始时回复10%的生命值</t>
+  </si>
+  <si>
+    <t>磨刀霍霍</t>
+  </si>
+  <si>
+    <t>MonsterGrow</t>
+  </si>
+  <si>
+    <t>本关内所有敌人每回合结束时攻击力+2</t>
+  </si>
+  <si>
+    <t>尖刺外壳</t>
+  </si>
+  <si>
+    <t>ThornShell</t>
+  </si>
+  <si>
+    <t>本关内玩家每次攻击敌人后,自身会受到该伤害15%的伤害</t>
+  </si>
+  <si>
+    <t>怨恨之灵</t>
+  </si>
+  <si>
+    <t>VengefulSoul</t>
+  </si>
+  <si>
+    <t>本关内敌人死亡后,会使玩家的攻击力永久降低2点</t>
+  </si>
+  <si>
+    <t>枯竭之泉</t>
+  </si>
+  <si>
+    <t>HealBan</t>
+  </si>
+  <si>
+    <t>本关内玩家受到的所有治疗与回复效果降低50%</t>
+  </si>
+  <si>
+    <t>苛刻裁判</t>
+  </si>
+  <si>
+    <t>TieLose</t>
+  </si>
+  <si>
+    <t>本关内比牌时双方牌型顺位一致时,敌人将获胜</t>
+  </si>
+  <si>
+    <t>背水一战</t>
+  </si>
+  <si>
+    <t>PhaseRage</t>
+  </si>
+  <si>
+    <t>0.5|2</t>
+  </si>
+  <si>
+    <t>本关内敌人生命值首次低于50%时,攻击力+50%,并获得2次伤害免疫</t>
+  </si>
+  <si>
+    <t>不灭传说</t>
+  </si>
+  <si>
+    <t>SecondWind</t>
+  </si>
+  <si>
+    <t>本关内敌人被击败时,将以30%的生命值复活一次</t>
+  </si>
+  <si>
+    <t>生命虹吸</t>
+  </si>
+  <si>
+    <t>LifeSiphon</t>
+  </si>
+  <si>
+    <t>本关内敌人攻击玩家时,按造成伤害的50%回复自身生命值</t>
   </si>
 </sst>
 </file>
@@ -488,12 +626,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -814,7 +958,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -838,16 +982,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -856,91 +1000,97 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -948,6 +1098,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1297,80 +1462,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="3.8" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.36666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.2166666666667" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.38333333333333" style="3" customWidth="1"/>
+    <col min="2" max="2" width="3.8" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.36666666666667" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14.2333333333333" style="3" customWidth="1"/>
+    <col min="5" max="5" width="7.39166666666667" style="3" customWidth="1"/>
+    <col min="6" max="6" width="25.2166666666667" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="B5" s="3">
+      <c r="B5" s="5">
         <v>101</v>
       </c>
       <c r="C5" t="s">
@@ -1379,7 +1544,7 @@
       <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
@@ -1387,16 +1552,16 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="B6" s="3">
+      <c r="B6" s="5">
         <v>102</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="5">
         <v>1</v>
       </c>
       <c r="F6" t="s">
@@ -1404,16 +1569,16 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="B7" s="3">
+      <c r="B7" s="5">
         <v>103</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="5">
         <v>1</v>
       </c>
       <c r="F7" t="s">
@@ -1421,16 +1586,16 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="B8" s="3">
+      <c r="B8" s="5">
         <v>104</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="5">
         <v>1</v>
       </c>
       <c r="F8" t="s">
@@ -1438,30 +1603,30 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="B9" s="3">
+      <c r="B9" s="5">
         <v>105</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="5">
         <v>1</v>
       </c>
       <c r="F9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="B10" s="3">
+    <row r="10" s="1" customFormat="1" spans="1:6">
+      <c r="B10" s="6">
         <v>106</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="7" t="s">
         <v>31</v>
       </c>
       <c r="E10" s="1">
@@ -1471,345 +1636,616 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="B11" s="3">
+    <row r="11" s="2" customFormat="1" spans="1:6">
+      <c r="B11" s="8">
         <v>107</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="1">
-        <v>-0.4</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="B12" s="3">
+      <c r="F11" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:6">
+      <c r="B12" s="8">
         <v>108</v>
       </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="C12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="1">
-        <v>-0.25</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="B13" s="3">
+      <c r="E12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="1:6">
+      <c r="B13" s="8">
         <v>109</v>
       </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="1">
-        <v>-0.5</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="E13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="B14" s="3">
+      <c r="B14" s="5">
         <v>110</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="3" t="s">
         <v>44</v>
+      </c>
+      <c r="E14" s="5">
+        <v>-0.1</v>
       </c>
       <c r="F14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="B15" s="3">
+    <row r="15" s="1" customFormat="1" spans="1:6">
+      <c r="B15" s="6">
         <v>111</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="6">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:6">
+      <c r="B16" s="6">
+        <v>112</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="2:7">
+      <c r="B17" s="8">
+        <v>113</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="2:7">
+      <c r="B18" s="6">
+        <v>114</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="2:7">
+      <c r="B19" s="8">
+        <v>115</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="8">
+        <v>3</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="2:7">
+      <c r="B20" s="8">
+        <v>116</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="2:7">
+      <c r="B21" s="8">
+        <v>117</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="2:7">
+      <c r="B22" s="6">
+        <v>118</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="6">
+        <v>4</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" spans="2:7">
+      <c r="B23" s="8">
+        <v>119</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" spans="2:7">
+      <c r="B24" s="8">
+        <v>120</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="8">
+        <v>2</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="2:7">
+      <c r="B25" s="8">
+        <v>121</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="8">
+        <v>5</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" spans="2:7">
+      <c r="B26" s="8">
+        <v>122</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="2:7">
+      <c r="B27" s="6">
+        <v>123</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="2:7">
+      <c r="B28" s="6">
+        <v>124</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="2:7">
+      <c r="B29" s="6">
+        <v>125</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" s="6">
+        <v>1</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="2:7">
+      <c r="B30" s="8">
+        <v>126</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G30" s="9"/>
+    </row>
+    <row r="31" s="2" customFormat="1" spans="2:7">
+      <c r="B31" s="8">
+        <v>127</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="G31" s="9"/>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="2:7">
+      <c r="B32" s="8">
+        <v>128</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" s="8">
+        <v>5</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G32" s="9"/>
+    </row>
+    <row r="33" s="2" customFormat="1" spans="2:7">
+      <c r="B33" s="8">
+        <v>129</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="G33" s="9"/>
+    </row>
+    <row r="34" s="2" customFormat="1" spans="2:7">
+      <c r="B34" s="8">
+        <v>130</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G34" s="9"/>
+    </row>
+    <row r="35" s="2" customFormat="1" spans="2:7">
+      <c r="B35" s="8">
+        <v>131</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E35" s="8">
+        <v>1</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="G35" s="9"/>
+    </row>
+    <row r="36" s="2" customFormat="1" spans="2:7">
+      <c r="B36" s="8">
+        <v>132</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E36" s="8">
+        <v>50</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="G36" s="9"/>
+    </row>
+    <row r="37" s="2" customFormat="1" spans="2:7">
+      <c r="B37" s="8">
+        <v>133</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="G37" s="9"/>
+    </row>
+    <row r="38" s="2" customFormat="1" spans="2:7">
+      <c r="B38" s="8">
+        <v>134</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38" s="8">
+        <v>2</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="G38" s="9"/>
+    </row>
+    <row r="39" s="2" customFormat="1" spans="2:7">
+      <c r="B39" s="8">
+        <v>135</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G39" s="9"/>
+    </row>
+    <row r="40" s="2" customFormat="1" spans="2:7">
+      <c r="B40" s="8">
+        <v>136</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-2</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G40" s="9"/>
+    </row>
+    <row r="41" s="2" customFormat="1" spans="2:7">
+      <c r="B41" s="8">
+        <v>137</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41" s="8">
         <v>-0.5</v>
       </c>
-      <c r="F15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="B16" s="3">
-        <v>112</v>
-      </c>
-      <c r="C16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="3">
+      <c r="F41" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G41" s="9"/>
+    </row>
+    <row r="42" s="2" customFormat="1" spans="2:7">
+      <c r="B42" s="8">
+        <v>138</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" s="8">
         <v>1</v>
       </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="3">
-        <v>113</v>
-      </c>
-      <c r="C17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" s="3">
-        <v>114</v>
-      </c>
-      <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" s="3">
-        <v>115</v>
-      </c>
-      <c r="C19" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="3">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="3">
-        <v>116</v>
-      </c>
-      <c r="C20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2</v>
-      </c>
-      <c r="F20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" s="3">
-        <v>117</v>
-      </c>
-      <c r="C21" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="B22" s="3">
-        <v>118</v>
-      </c>
-      <c r="C22" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" t="s">
-        <v>69</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6">
-      <c r="B23" s="3">
-        <v>119</v>
-      </c>
-      <c r="C23" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" s="3">
-        <v>4</v>
-      </c>
-      <c r="F23" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="B24" s="3">
-        <v>120</v>
-      </c>
-      <c r="C24" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F24" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="B25" s="3">
-        <v>121</v>
-      </c>
-      <c r="C25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" s="3">
-        <v>4</v>
-      </c>
-      <c r="F25" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="B26" s="3">
-        <v>122</v>
-      </c>
-      <c r="C26" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" t="s">
-        <v>83</v>
-      </c>
-      <c r="E26" s="3">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="B27" s="3">
-        <v>123</v>
-      </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>86</v>
-      </c>
-      <c r="E27" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="F27" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6">
-      <c r="B28" s="3">
-        <v>124</v>
-      </c>
-      <c r="C28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" s="3">
-        <v>1</v>
-      </c>
-      <c r="F28" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="B29" s="3">
-        <v>125</v>
-      </c>
-      <c r="C29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" s="3">
-        <v>1</v>
-      </c>
-      <c r="F29" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
-      <c r="B30" s="3">
-        <v>126</v>
-      </c>
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" s="3">
-        <v>1</v>
-      </c>
-      <c r="F30" t="s">
-        <v>96</v>
-      </c>
+      <c r="F42" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="G42" s="9"/>
+    </row>
+    <row r="43" s="2" customFormat="1" spans="2:7">
+      <c r="B43" s="8">
+        <v>139</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="G43" s="9"/>
+    </row>
+    <row r="44" s="2" customFormat="1" spans="2:7">
+      <c r="B44" s="8">
+        <v>140</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="G44" s="9"/>
+    </row>
+    <row r="45" s="2" customFormat="1" spans="2:7">
+      <c r="B45" s="8">
+        <v>141</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="G45" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/BossEntryConfig.xlsx
+++ b/Config/BossEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="13695" windowHeight="11505"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="145">
   <si>
     <t>##var</t>
   </si>
@@ -73,12 +73,198 @@
     <t>机制类型</t>
   </si>
   <si>
-    <t>值</t>
+    <t>生效值</t>
   </si>
   <si>
     <t>描述</t>
   </si>
   <si>
+    <t>诅咒之躯</t>
+  </si>
+  <si>
+    <t>CurseBody</t>
+  </si>
+  <si>
+    <t>0|0.1</t>
+  </si>
+  <si>
+    <t>玩家在本关内每次攻击敌人时,会使自身的血量扣除10%</t>
+  </si>
+  <si>
+    <t>钝化之躯</t>
+  </si>
+  <si>
+    <t>PlayerDamageDown</t>
+  </si>
+  <si>
+    <t>玩家在本关内造成的伤害-30%</t>
+  </si>
+  <si>
+    <t>隐身之躯</t>
+  </si>
+  <si>
+    <t>SkillDisable</t>
+  </si>
+  <si>
+    <t>本关内无法使用[透视]技能</t>
+  </si>
+  <si>
+    <t>手牌烙印</t>
+  </si>
+  <si>
+    <t>HandBrand</t>
+  </si>
+  <si>
+    <t>本关内玩家亮出的牌中随机有1张牌的点数将不提供攻击力</t>
+  </si>
+  <si>
+    <t>灵活身姿</t>
+  </si>
+  <si>
+    <t>MonsterEvade</t>
+  </si>
+  <si>
+    <t>本关内所有敌人拥有40%闪避率</t>
+  </si>
+  <si>
+    <t>痛击</t>
+  </si>
+  <si>
+    <t>MonsterDamageUp</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>本关内所有敌人造成的伤害+50%</t>
+  </si>
+  <si>
+    <t>禁用圣物</t>
+  </si>
+  <si>
+    <t>RelicDisable</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>本关内将随机失效2件玩家所持有的圣物效果</t>
+  </si>
+  <si>
+    <t>经济黑洞</t>
+  </si>
+  <si>
+    <t>0.1|0.2</t>
+  </si>
+  <si>
+    <t>本关内敌人造成的伤害+10%,且每轮开始时都会使玩家失去当前20%的金币</t>
+  </si>
+  <si>
+    <t>脆弱身躯</t>
+  </si>
+  <si>
+    <t>FragileBody</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>本关内玩家承受的伤害+20%,且无法通过任何手段恢复生命值</t>
+  </si>
+  <si>
+    <t>手牌压缩</t>
+  </si>
+  <si>
+    <t>HandCompress</t>
+  </si>
+  <si>
+    <t>本关内玩家每回合的手牌数量从5张降低至4张</t>
+  </si>
+  <si>
+    <t>狂暴增长</t>
+  </si>
+  <si>
+    <t>MonsterRage</t>
+  </si>
+  <si>
+    <t>0.2|0.2</t>
+  </si>
+  <si>
+    <t>本关内敌人每损失20%生命值,其攻击力+20%</t>
+  </si>
+  <si>
+    <t>黑暗护盾</t>
+  </si>
+  <si>
+    <t>MonsterShield</t>
+  </si>
+  <si>
+    <t>本关内敌人会免疫首次受到的伤害</t>
+  </si>
+  <si>
+    <t>回合制约</t>
+  </si>
+  <si>
+    <t>RoundLimit</t>
+  </si>
+  <si>
+    <t>本关内将限制回合数为5,若玩家5回合内未击杀所有敌人,将立即死亡</t>
+  </si>
+  <si>
+    <t>窃取指环</t>
+  </si>
+  <si>
+    <t>AttackSteal</t>
+  </si>
+  <si>
+    <t>本关内每回合开始时,随机1名敌人会偷取玩家当前5%的血量</t>
+  </si>
+  <si>
+    <t>禁用红心</t>
+  </si>
+  <si>
+    <t>DisableHeartUesd</t>
+  </si>
+  <si>
+    <t>本关内玩家手上的红心牌将失效[无法凑成牌型、无法提供攻击力]</t>
+  </si>
+  <si>
+    <t>禁用黑桃</t>
+  </si>
+  <si>
+    <t>DisableSpadeUesd</t>
+  </si>
+  <si>
+    <t>本关内玩家手上的黑桃牌将失效[无法凑成牌型、无法提供攻击力]</t>
+  </si>
+  <si>
+    <t>禁用方片</t>
+  </si>
+  <si>
+    <t>DisableDiamonUesdd</t>
+  </si>
+  <si>
+    <t>本关内玩家手上的方片牌将失效[无法凑成牌型、无法提供攻击力]</t>
+  </si>
+  <si>
+    <t>禁用梅花</t>
+  </si>
+  <si>
+    <t>DisablePlumBlossomUesd</t>
+  </si>
+  <si>
+    <t>本关内玩家手上的梅花牌将失效[无法凑成牌型、无法提供攻击力]</t>
+  </si>
+  <si>
+    <t>禁用人头</t>
+  </si>
+  <si>
+    <t>DisableHeadUesd</t>
+  </si>
+  <si>
+    <t>本关内玩家手上的人头牌将失效[无法凑成牌型、无法提供攻击力]</t>
+  </si>
+  <si>
     <t>禁搓红心</t>
   </si>
   <si>
@@ -94,6 +280,9 @@
     <t>DisableSpade</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>本关内搓牌时,无法出现黑桃花色</t>
   </si>
   <si>
@@ -124,214 +313,31 @@
     <t>本关内搓牌时,无法出现人头牌</t>
   </si>
   <si>
-    <t>钝化之躯</t>
-  </si>
-  <si>
-    <t>PlayerDamageDown</t>
-  </si>
-  <si>
-    <t>本关内玩家造成的伤害-50%</t>
-  </si>
-  <si>
-    <t>禁用同花</t>
+    <t>同花削弱</t>
   </si>
   <si>
     <t>FlushDamage</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>本关内亮出同花牌型时,将无法造成伤害</t>
-  </si>
-  <si>
-    <t>禁用对子</t>
+    <t>本关内亮出同花牌型时,伤害-50%</t>
+  </si>
+  <si>
+    <t>顺子削弱</t>
+  </si>
+  <si>
+    <t>StraightDamage</t>
+  </si>
+  <si>
+    <t>本关内亮出顺子牌型时,伤害-50%</t>
+  </si>
+  <si>
+    <t>对子削弱</t>
   </si>
   <si>
     <t>CoupletDamage</t>
   </si>
   <si>
-    <t>本关内亮出对子牌型时,将无法造成伤害</t>
-  </si>
-  <si>
-    <t>禁用顺子</t>
-  </si>
-  <si>
-    <t>StraightDamage</t>
-  </si>
-  <si>
-    <t>本关内亮出顺子牌型时,将无法造成伤害</t>
-  </si>
-  <si>
-    <t>诅咒之躯</t>
-  </si>
-  <si>
-    <t>CurseBody</t>
-  </si>
-  <si>
-    <t>本关内玩家每次攻击敌人时,会使自身的血量扣除10%</t>
-  </si>
-  <si>
-    <t>失效光环</t>
-  </si>
-  <si>
-    <t>SkillDisable</t>
-  </si>
-  <si>
-    <t>本关内无法使用任何技能[搓牌/透视/替换]</t>
-  </si>
-  <si>
-    <t>手牌烙印</t>
-  </si>
-  <si>
-    <t>HandBrand</t>
-  </si>
-  <si>
-    <t>本关内玩家亮出的手牌中将有1张不参与牌型构成</t>
-  </si>
-  <si>
-    <t>灵活身姿</t>
-  </si>
-  <si>
-    <t>MonsterEvade</t>
-  </si>
-  <si>
-    <t>0.6|0.1</t>
-  </si>
-  <si>
-    <t>本关内所有敌人拥有60%闪避率,且每次成功闪避时都会使自身攻击力+10%</t>
-  </si>
-  <si>
-    <t>双倍痛击</t>
-  </si>
-  <si>
-    <t>MonsterDamageUp</t>
-  </si>
-  <si>
-    <t>本关内所有敌人造成的伤害+100%</t>
-  </si>
-  <si>
-    <t>禁用遗物</t>
-  </si>
-  <si>
-    <t>RelicDisable</t>
-  </si>
-  <si>
-    <t>本关内将随机失效3件玩家所拥有的遗物效果</t>
-  </si>
-  <si>
-    <t>经济黑洞</t>
-  </si>
-  <si>
-    <t>GoldThorn</t>
-  </si>
-  <si>
-    <t>0.3|-0.5</t>
-  </si>
-  <si>
-    <t>本关内敌人造成的伤害+30%,且每回合开始时都会失去当前50%的金币</t>
-  </si>
-  <si>
-    <t>脆弱身躯</t>
-  </si>
-  <si>
-    <t>FragileBody</t>
-  </si>
-  <si>
-    <t>本关内玩家承受的伤害+50%,且无法通过任何手段恢复生命值</t>
-  </si>
-  <si>
-    <t>手牌压缩</t>
-  </si>
-  <si>
-    <t>HandCompress</t>
-  </si>
-  <si>
-    <t>本关内玩家每回合的手牌数量从5张降低至4张</t>
-  </si>
-  <si>
-    <t>狂暴增长</t>
-  </si>
-  <si>
-    <t>MonsterRage</t>
-  </si>
-  <si>
-    <t>0.2|0.5</t>
-  </si>
-  <si>
-    <t>本关内敌人每损失20%生命值,其攻击力+50%</t>
-  </si>
-  <si>
-    <t>黑暗护盾</t>
-  </si>
-  <si>
-    <t>MonsterShield</t>
-  </si>
-  <si>
-    <t>本关内BOSS会免疫前2次受到的所有伤害</t>
-  </si>
-  <si>
-    <t>回合制约</t>
-  </si>
-  <si>
-    <t>RoundLimit</t>
-  </si>
-  <si>
-    <t>本关内将限制回合数为5,若5回合内未击杀所有敌人,将立即死亡</t>
-  </si>
-  <si>
-    <t>窃取指环</t>
-  </si>
-  <si>
-    <t>AttackSteal</t>
-  </si>
-  <si>
-    <t>本关内每回合开始时,随机1名敌人会偷取玩家当前10%的攻击力</t>
-  </si>
-  <si>
-    <t>胆小首领</t>
-  </si>
-  <si>
-    <t>BossTimid</t>
-  </si>
-  <si>
-    <t>本关内在非BOSS敌人死亡前,BOSS将免疫受到的所有伤害</t>
-  </si>
-  <si>
-    <t>方片红桃</t>
-  </si>
-  <si>
-    <t>DisableRedSuit</t>
-  </si>
-  <si>
-    <t>本关内玩家手上的方片和红桃牌将失效[无法凑成牌型、无法提供攻击力]</t>
-  </si>
-  <si>
-    <t>黑桃梅花</t>
-  </si>
-  <si>
-    <t>DisableBlackSuit</t>
-  </si>
-  <si>
-    <t>本关内玩家手上的黑桃和梅花牌将失效[无法凑成牌型、无法提供攻击力]</t>
-  </si>
-  <si>
-    <t>禁搓偶数</t>
-  </si>
-  <si>
-    <t>DisableEven</t>
-  </si>
-  <si>
-    <t>本关内搓牌时,无法出现偶数点数的牌</t>
-  </si>
-  <si>
-    <t>禁搓A</t>
-  </si>
-  <si>
-    <t>DisableAce</t>
-  </si>
-  <si>
-    <t>本关内搓牌时,无法出现A</t>
+    <t>本关内亮出对子牌型时,伤害-50%</t>
   </si>
   <si>
     <t>王权旁落</t>
@@ -358,7 +364,7 @@
     <t>RubDown</t>
   </si>
   <si>
-    <t>本关内搓牌次数减少1次</t>
+    <t>本关内[搓牌]次数减少1次</t>
   </si>
   <si>
     <t>宿命之手</t>
@@ -367,7 +373,7 @@
     <t>SwapLock</t>
   </si>
   <si>
-    <t>本关内无法使用换牌技能</t>
+    <t>本关内无法使用[替换]技能</t>
   </si>
   <si>
     <t>有偿服务</t>
@@ -376,7 +382,7 @@
     <t>RubFee</t>
   </si>
   <si>
-    <t>本关内每次搓牌需要消耗50金币,金币不足时无法搓牌</t>
+    <t>本关内使用[搓牌]技能需要消耗50金币,金币不足时无法使用</t>
   </si>
   <si>
     <t>巫术灵体</t>
@@ -385,7 +391,7 @@
     <t>MonsterRegen</t>
   </si>
   <si>
-    <t>本关内所有敌人每回合开始时回复10%的生命值</t>
+    <t>本关内敌人每回合开始时回复10%的血量</t>
   </si>
   <si>
     <t>磨刀霍霍</t>
@@ -403,7 +409,7 @@
     <t>ThornShell</t>
   </si>
   <si>
-    <t>本关内玩家每次攻击敌人后,自身会受到该伤害15%的伤害</t>
+    <t>本关内玩家每次攻击敌人后,自身会受到该伤害5%的伤害</t>
   </si>
   <si>
     <t>怨恨之灵</t>
@@ -412,7 +418,7 @@
     <t>VengefulSoul</t>
   </si>
   <si>
-    <t>本关内敌人死亡后,会使玩家的攻击力永久降低2点</t>
+    <t>本关内敌人死亡后,会使玩家的攻击力永久降低1点</t>
   </si>
   <si>
     <t>枯竭之泉</t>
@@ -439,10 +445,10 @@
     <t>PhaseRage</t>
   </si>
   <si>
-    <t>0.5|2</t>
-  </si>
-  <si>
-    <t>本关内敌人生命值首次低于50%时,攻击力+50%,并获得2次伤害免疫</t>
+    <t>0.5|0.5</t>
+  </si>
+  <si>
+    <t>本关内敌人生命值首次低于50%时,攻击力+50%</t>
   </si>
   <si>
     <t>不灭传说</t>
@@ -451,7 +457,7 @@
     <t>SecondWind</t>
   </si>
   <si>
-    <t>本关内敌人被击败时,将以30%的生命值复活一次</t>
+    <t>本关内敌人被击败时,将以20%的血量复活一次</t>
   </si>
   <si>
     <t>生命虹吸</t>
@@ -460,7 +466,7 @@
     <t>LifeSiphon</t>
   </si>
   <si>
-    <t>本关内敌人攻击玩家时,按造成伤害的50%回复自身生命值</t>
+    <t>本关内敌人攻击玩家时,按造成伤害的25%回复自身血量</t>
   </si>
 </sst>
 </file>
@@ -1082,12 +1088,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1099,19 +1102,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1465,77 +1459,77 @@
   <dimension ref="A1:G45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="2.38333333333333" style="3" customWidth="1"/>
-    <col min="2" max="2" width="3.8" style="3" customWidth="1"/>
-    <col min="3" max="3" width="8.36666666666667" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14.2333333333333" style="3" customWidth="1"/>
-    <col min="5" max="5" width="7.39166666666667" style="3" customWidth="1"/>
-    <col min="6" max="6" width="25.2166666666667" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="3" customWidth="1"/>
+    <col min="1" max="1" width="2.38333333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="3.8" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.36666666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.2333333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.39166666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.2166666666667" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>101</v>
       </c>
       <c r="C5" t="s">
@@ -1544,708 +1538,708 @@
       <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="5">
-        <v>1</v>
+      <c r="E5" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:6">
       <c r="B6" s="5">
         <v>102</v>
       </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="E6" s="5">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>-0.3</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:6">
       <c r="B7" s="5">
         <v>103</v>
       </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="6" t="s">
         <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E7" s="5">
         <v>1</v>
       </c>
-      <c r="F7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:6">
       <c r="B8" s="5">
         <v>104</v>
       </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="C8" s="6" t="s">
         <v>25</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="E8" s="5">
         <v>1</v>
       </c>
-      <c r="F8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="F8" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:6">
       <c r="B9" s="5">
         <v>105</v>
       </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="C9" s="6" t="s">
         <v>28</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E9" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:6">
+      <c r="B10" s="5">
+        <v>106</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:6">
+      <c r="B11" s="5">
+        <v>107</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:6">
+      <c r="B12" s="5">
+        <v>108</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:6">
+      <c r="B13" s="5">
+        <v>109</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:6">
+      <c r="B14" s="4">
+        <v>110</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="4">
+        <v>4</v>
+      </c>
+      <c r="F14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:6">
+      <c r="B15" s="4">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:6">
+      <c r="B16" s="4">
+        <v>112</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="4">
         <v>1</v>
       </c>
-      <c r="F9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:6">
-      <c r="B10" s="6">
+      <c r="F16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="2:7">
+      <c r="B17" s="4">
+        <v>113</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="4">
+        <v>5</v>
+      </c>
+      <c r="F17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="2:7">
+      <c r="B18" s="5">
+        <v>114</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="2:7">
+      <c r="B19" s="5">
+        <v>115</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="5">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="2:7">
+      <c r="B20" s="5">
+        <v>116</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="5">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="2:7">
+      <c r="B21" s="5">
+        <v>117</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="2:7">
+      <c r="B22" s="5">
+        <v>118</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="2:7">
+      <c r="B23" s="5">
+        <v>119</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="5">
+        <v>1</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="2:7">
+      <c r="B24" s="5">
+        <v>120</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="5">
+        <v>1</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="2:7">
+      <c r="B25" s="5">
+        <v>121</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="2:7">
+      <c r="B26" s="5">
+        <v>122</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="2:7">
+      <c r="B27" s="5">
+        <v>123</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="2:7">
+      <c r="B28" s="5">
+        <v>124</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="2:7">
+      <c r="B29" s="5">
+        <v>125</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" s="5">
+        <v>-0.5</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="2:7">
+      <c r="B30" s="5">
+        <v>126</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" s="5">
+        <v>-0.5</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G30" s="6"/>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="2:7">
+      <c r="B31" s="5">
+        <v>127</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" s="5">
+        <v>-0.5</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" s="6"/>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="2:7">
+      <c r="B32" s="5">
+        <v>128</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" s="5">
+        <v>5</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G32" s="6"/>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="2:7">
+      <c r="B33" s="5">
+        <v>129</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="E33" s="5">
+        <v>1</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G33" s="6"/>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="2:7">
+      <c r="B34" s="5">
+        <v>130</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E34" s="5">
+        <v>1</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" s="6"/>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="2:7">
+      <c r="B35" s="5">
+        <v>131</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E35" s="5">
+        <v>1</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="2:7">
+      <c r="B36" s="5">
+        <v>132</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E36" s="5">
+        <v>50</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="2:7">
+      <c r="B37" s="5">
+        <v>133</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="2:7">
+      <c r="B38" s="5">
+        <v>134</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E38" s="5">
+        <v>2</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="2:7">
+      <c r="B39" s="5">
+        <v>135</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="2:7">
+      <c r="B40" s="5">
+        <v>136</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E40" s="5">
+        <v>-1</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="2:7">
+      <c r="B41" s="5">
+        <v>137</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41" s="5">
         <v>-0.5</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:6">
-      <c r="B11" s="8">
-        <v>107</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:6">
-      <c r="B12" s="8">
-        <v>108</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:6">
-      <c r="B13" s="8">
-        <v>109</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="B14" s="5">
-        <v>110</v>
-      </c>
-      <c r="C14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="5">
-        <v>-0.1</v>
-      </c>
-      <c r="F14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:6">
-      <c r="B15" s="6">
-        <v>111</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="F41" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="2:7">
+      <c r="B42" s="5">
+        <v>138</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E42" s="5">
         <v>1</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:6">
-      <c r="B16" s="6">
-        <v>112</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="6">
-        <v>1</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="2:7">
-      <c r="B17" s="8">
-        <v>113</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="2:7">
-      <c r="B18" s="6">
-        <v>114</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="2:7">
-      <c r="B19" s="8">
-        <v>115</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="8">
-        <v>3</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="2:7">
-      <c r="B20" s="8">
-        <v>116</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="2:7">
-      <c r="B21" s="8">
-        <v>117</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="2:7">
-      <c r="B22" s="6">
-        <v>118</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="6">
-        <v>4</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="2:7">
-      <c r="B23" s="8">
-        <v>119</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="2:7">
-      <c r="B24" s="8">
-        <v>120</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="8">
-        <v>2</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="2:7">
-      <c r="B25" s="8">
-        <v>121</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" s="8">
-        <v>5</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="2:7">
-      <c r="B26" s="8">
-        <v>122</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="2:7">
-      <c r="B27" s="6">
-        <v>123</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E27" s="6">
-        <v>1</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="2:7">
-      <c r="B28" s="6">
-        <v>124</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" s="6">
-        <v>1</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="2:7">
-      <c r="B29" s="6">
-        <v>125</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" s="6">
-        <v>1</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="2:7">
-      <c r="B30" s="8">
-        <v>126</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="G30" s="9"/>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="2:7">
-      <c r="B31" s="8">
-        <v>127</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="G31" s="9"/>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="2:7">
-      <c r="B32" s="8">
-        <v>128</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E32" s="8">
-        <v>5</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="G32" s="9"/>
-    </row>
-    <row r="33" s="2" customFormat="1" spans="2:7">
-      <c r="B33" s="8">
-        <v>129</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G33" s="9"/>
-    </row>
-    <row r="34" s="2" customFormat="1" spans="2:7">
-      <c r="B34" s="8">
-        <v>130</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" s="8">
-        <v>1</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="G34" s="9"/>
-    </row>
-    <row r="35" s="2" customFormat="1" spans="2:7">
-      <c r="B35" s="8">
-        <v>131</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E35" s="8">
-        <v>1</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="G35" s="9"/>
-    </row>
-    <row r="36" s="2" customFormat="1" spans="2:7">
-      <c r="B36" s="8">
-        <v>132</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" s="8">
-        <v>50</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="G36" s="9"/>
-    </row>
-    <row r="37" s="2" customFormat="1" spans="2:7">
-      <c r="B37" s="8">
-        <v>133</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="G37" s="9"/>
-    </row>
-    <row r="38" s="2" customFormat="1" spans="2:7">
-      <c r="B38" s="8">
+      <c r="F42" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="E38" s="8">
-        <v>2</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="G38" s="9"/>
-    </row>
-    <row r="39" s="2" customFormat="1" spans="2:7">
-      <c r="B39" s="8">
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="2:7">
+      <c r="B43" s="5">
+        <v>139</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="G39" s="9"/>
-    </row>
-    <row r="40" s="2" customFormat="1" spans="2:7">
-      <c r="B40" s="8">
+      <c r="D43" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-2</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="G40" s="9"/>
-    </row>
-    <row r="41" s="2" customFormat="1" spans="2:7">
-      <c r="B41" s="8">
+      <c r="E43" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.5</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="G41" s="9"/>
-    </row>
-    <row r="42" s="2" customFormat="1" spans="2:7">
-      <c r="B42" s="8">
+      <c r="F43" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E42" s="8">
-        <v>1</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="G42" s="9"/>
-    </row>
-    <row r="43" s="2" customFormat="1" spans="2:7">
-      <c r="B43" s="8">
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" s="1" customFormat="1" spans="2:7">
+      <c r="B44" s="5">
+        <v>140</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="G43" s="9"/>
-    </row>
-    <row r="44" s="2" customFormat="1" spans="2:7">
-      <c r="B44" s="8">
+      <c r="D44" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.3</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="G44" s="9"/>
-    </row>
-    <row r="45" s="2" customFormat="1" spans="2:7">
-      <c r="B45" s="8">
+      <c r="E44" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="F44" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="D45" s="10" t="s">
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="2:7">
+      <c r="B45" s="5">
         <v>141</v>
       </c>
-      <c r="E45" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="F45" s="10" t="s">
+      <c r="C45" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G45" s="9"/>
+      <c r="D45" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E45" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G45" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/BossEntryConfig.xlsx
+++ b/Config/BossEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="17910" windowHeight="10440"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="141">
   <si>
     <t>##var</t>
   </si>
@@ -85,10 +85,10 @@
     <t>CurseBody</t>
   </si>
   <si>
-    <t>0|0.1</t>
-  </si>
-  <si>
-    <t>玩家在本关内每次攻击敌人时,会使自身的血量扣除10%</t>
+    <t>0|0.05</t>
+  </si>
+  <si>
+    <t>玩家在本关内每次攻击敌人时,会使自身的血量扣除5%</t>
   </si>
   <si>
     <t>钝化之躯</t>
@@ -106,16 +106,7 @@
     <t>SkillDisable</t>
   </si>
   <si>
-    <t>本关内无法使用[透视]技能</t>
-  </si>
-  <si>
-    <t>手牌烙印</t>
-  </si>
-  <si>
-    <t>HandBrand</t>
-  </si>
-  <si>
-    <t>本关内玩家亮出的牌中随机有1张牌的点数将不提供攻击力</t>
+    <t>本关内无法使用任何技能</t>
   </si>
   <si>
     <t>灵活身姿</t>
@@ -133,10 +124,7 @@
     <t>MonsterDamageUp</t>
   </si>
   <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>本关内所有敌人造成的伤害+50%</t>
+    <t>本关内所有敌人造成的伤害+25%</t>
   </si>
   <si>
     <t>禁用圣物</t>
@@ -208,7 +196,7 @@
     <t>RoundLimit</t>
   </si>
   <si>
-    <t>本关内将限制回合数为5,若玩家5回合内未击杀所有敌人,将立即死亡</t>
+    <t>本关内将限制回合数为7,若玩家7回合内未击杀所有敌人,将立即死亡</t>
   </si>
   <si>
     <t>窃取指环</t>
@@ -217,7 +205,7 @@
     <t>AttackSteal</t>
   </si>
   <si>
-    <t>本关内每回合开始时,随机1名敌人会偷取玩家当前5%的血量</t>
+    <t>本关内每回合开始时,随机1名敌人会偷取玩家当前5%的攻击力</t>
   </si>
   <si>
     <t>禁用红心</t>
@@ -409,7 +397,7 @@
     <t>ThornShell</t>
   </si>
   <si>
-    <t>本关内玩家每次攻击敌人后,自身会受到该伤害5%的伤害</t>
+    <t>本关内玩家每次攻击敌人后,自身会受到该伤害10%的伤害</t>
   </si>
   <si>
     <t>怨恨之灵</t>
@@ -418,7 +406,7 @@
     <t>VengefulSoul</t>
   </si>
   <si>
-    <t>本关内敌人死亡后,会使玩家的攻击力永久降低1点</t>
+    <t>本关内敌人死亡后,会使玩家的攻击力永久降低2点</t>
   </si>
   <si>
     <t>枯竭之泉</t>
@@ -1456,7 +1444,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="2.38333333333333" style="2" customWidth="1"/>
@@ -1590,7 +1578,7 @@
         <v>26</v>
       </c>
       <c r="E8" s="5">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>27</v>
@@ -1603,11 +1591,11 @@
       <c r="C9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="5">
-        <v>0.4</v>
+      <c r="E9" s="1">
+        <v>0.25</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>30</v>
@@ -1620,7 +1608,7 @@
       <c r="C10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1638,13 +1626,13 @@
         <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:6">
@@ -1652,10 +1640,10 @@
         <v>108</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>40</v>
@@ -1664,21 +1652,21 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:6">
-      <c r="B13" s="5">
+    <row r="13" s="2" customFormat="1" spans="1:6">
+      <c r="B13" s="4">
         <v>109</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="4">
+        <v>4</v>
+      </c>
+      <c r="F13" t="s">
         <v>44</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" spans="1:6">
@@ -1686,13 +1674,13 @@
         <v>110</v>
       </c>
       <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
         <v>46</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="E14" s="4">
-        <v>4</v>
       </c>
       <c r="F14" t="s">
         <v>48</v>
@@ -1708,11 +1696,11 @@
       <c r="D15" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
         <v>51</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:6">
@@ -1720,33 +1708,33 @@
         <v>112</v>
       </c>
       <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
         <v>53</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" s="4">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="4">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
+    </row>
+    <row r="17" s="1" customFormat="1" spans="2:7">
+      <c r="B17" s="5">
+        <v>113</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="2:7">
-      <c r="B17" s="4">
-        <v>113</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D17" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="E17" s="4">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="2:7">
@@ -1754,16 +1742,16 @@
         <v>114</v>
       </c>
       <c r="C18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="E18" s="5">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="E18" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="2:7">
@@ -1771,16 +1759,16 @@
         <v>115</v>
       </c>
       <c r="C19" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="E19" s="5">
         <v>1</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="2:7">
@@ -1788,16 +1776,16 @@
         <v>116</v>
       </c>
       <c r="C20" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="E20" s="5">
         <v>1</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="2:7">
@@ -1805,16 +1793,16 @@
         <v>117</v>
       </c>
       <c r="C21" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="E21" s="5">
         <v>1</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="2:7">
@@ -1822,16 +1810,16 @@
         <v>118</v>
       </c>
       <c r="C22" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="E22" s="5">
         <v>1</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="2:7">
@@ -1839,16 +1827,16 @@
         <v>119</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="E23" s="5">
         <v>1</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="2:7">
@@ -1856,13 +1844,13 @@
         <v>120</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="E24" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="E24" s="5">
-        <v>1</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>79</v>
@@ -1879,10 +1867,10 @@
         <v>81</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="2:7">
@@ -1890,16 +1878,16 @@
         <v>122</v>
       </c>
       <c r="C26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="2:7">
@@ -1907,16 +1895,16 @@
         <v>123</v>
       </c>
       <c r="C27" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="2:7">
@@ -1924,16 +1912,16 @@
         <v>124</v>
       </c>
       <c r="C28" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="5">
+        <v>-0.5</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="2:7">
@@ -1941,33 +1929,34 @@
         <v>125</v>
       </c>
       <c r="C29" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>94</v>
       </c>
       <c r="E29" s="5">
         <v>-0.5</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>95</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="G29" s="6"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="2:7">
       <c r="B30" s="5">
         <v>126</v>
       </c>
       <c r="C30" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="E30" s="5">
         <v>-0.5</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G30" s="6"/>
     </row>
@@ -1976,16 +1965,16 @@
         <v>127</v>
       </c>
       <c r="C31" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="E31" s="5">
+        <v>5</v>
+      </c>
+      <c r="F31" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="E31" s="5">
-        <v>-0.5</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="G31" s="6"/>
     </row>
@@ -1994,16 +1983,16 @@
         <v>128</v>
       </c>
       <c r="C32" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="E32" s="5">
+        <v>1</v>
+      </c>
+      <c r="F32" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="E32" s="5">
-        <v>5</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="G32" s="6"/>
     </row>
@@ -2012,16 +2001,16 @@
         <v>129</v>
       </c>
       <c r="C33" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="E33" s="5">
         <v>1</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G33" s="6"/>
     </row>
@@ -2030,16 +2019,16 @@
         <v>130</v>
       </c>
       <c r="C34" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="E34" s="5">
         <v>1</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G34" s="6"/>
     </row>
@@ -2048,16 +2037,16 @@
         <v>131</v>
       </c>
       <c r="C35" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="E35" s="5">
+        <v>50</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="E35" s="5">
-        <v>1</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="G35" s="6"/>
     </row>
@@ -2066,16 +2055,16 @@
         <v>132</v>
       </c>
       <c r="C36" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="E36" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="E36" s="5">
-        <v>50</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="G36" s="6"/>
     </row>
@@ -2084,16 +2073,16 @@
         <v>133</v>
       </c>
       <c r="C37" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="E37" s="5">
+        <v>2</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="E37" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="G37" s="6"/>
     </row>
@@ -2102,16 +2091,16 @@
         <v>134</v>
       </c>
       <c r="C38" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="E38" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="F38" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="E38" s="5">
-        <v>2</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="G38" s="6"/>
     </row>
@@ -2120,16 +2109,16 @@
         <v>135</v>
       </c>
       <c r="C39" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="E39" s="5">
+        <v>-2</v>
+      </c>
+      <c r="F39" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="E39" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="G39" s="6"/>
     </row>
@@ -2138,16 +2127,16 @@
         <v>136</v>
       </c>
       <c r="C40" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="E40" s="5">
+        <v>-0.5</v>
+      </c>
+      <c r="F40" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="E40" s="5">
-        <v>-1</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="G40" s="6"/>
     </row>
@@ -2156,16 +2145,16 @@
         <v>137</v>
       </c>
       <c r="C41" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="E41" s="5">
+        <v>1</v>
+      </c>
+      <c r="F41" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="E41" s="5">
-        <v>-0.5</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>131</v>
       </c>
       <c r="G41" s="6"/>
     </row>
@@ -2174,13 +2163,13 @@
         <v>138</v>
       </c>
       <c r="C42" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="E42" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="E42" s="5">
-        <v>1</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>134</v>
@@ -2197,11 +2186,11 @@
       <c r="D43" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="F43" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="G43" s="6"/>
     </row>
@@ -2210,36 +2199,18 @@
         <v>140</v>
       </c>
       <c r="C44" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="E44" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="F44" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="E44" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="G44" s="6"/>
-    </row>
-    <row r="45" s="1" customFormat="1" spans="2:7">
-      <c r="B45" s="5">
-        <v>141</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="E45" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G45" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/BossEntryConfig.xlsx
+++ b/Config/BossEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17910" windowHeight="10440"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="135">
   <si>
     <t>##var</t>
   </si>
@@ -328,24 +328,6 @@
     <t>本关内亮出对子牌型时,伤害-50%</t>
   </si>
   <si>
-    <t>王权旁落</t>
-  </si>
-  <si>
-    <t>FaceDevalue</t>
-  </si>
-  <si>
-    <t>本关内人头牌[J/Q/K]伤害点数按5计算,比牌大小不变</t>
-  </si>
-  <si>
-    <t>折翼之A</t>
-  </si>
-  <si>
-    <t>AceDown</t>
-  </si>
-  <si>
-    <t>本关内A的伤害点数由11降为1,比牌大小不变</t>
-  </si>
-  <si>
     <t>生锈拇指</t>
   </si>
   <si>
@@ -370,7 +352,7 @@
     <t>RubFee</t>
   </si>
   <si>
-    <t>本关内使用[搓牌]技能需要消耗50金币,金币不足时无法使用</t>
+    <t>本关内使用[搓牌]技能需要消耗100金币,金币不足时无法使用</t>
   </si>
   <si>
     <t>巫术灵体</t>
@@ -1091,10 +1073,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1444,7 +1426,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="2.38333333333333" style="2" customWidth="1"/>
@@ -1534,78 +1516,78 @@
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:6">
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>102</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="6">
         <v>-0.3</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:6">
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>103</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="6">
         <v>1</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:6">
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>104</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="6">
         <v>0.4</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:6">
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>105</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E9" s="1">
         <v>0.25</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:6">
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>106</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -1614,15 +1596,15 @@
       <c r="E10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:6">
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>107</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -1631,15 +1613,15 @@
       <c r="E11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:6">
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>108</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1648,7 +1630,7 @@
       <c r="E12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1721,129 +1703,129 @@
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="2:7">
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>113</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="6">
         <v>0.05</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="5" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="2:7">
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>114</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="6">
         <v>1</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="2:7">
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>115</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="6">
         <v>1</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="2:7">
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>116</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="6">
         <v>1</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="2:7">
-      <c r="B21" s="5">
+      <c r="B21" s="4">
         <v>117</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>67</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="6">
         <v>1</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="5" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="2:7">
-      <c r="B22" s="5">
+      <c r="B22" s="4">
         <v>118</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>70</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="6">
         <v>1</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="5" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="2:7">
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>119</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="6">
         <v>1</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="5" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="2:7">
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>120</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -1852,15 +1834,15 @@
       <c r="E24" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="2:7">
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <v>121</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="5" t="s">
         <v>80</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -1869,15 +1851,15 @@
       <c r="E25" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="5" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="2:7">
-      <c r="B26" s="5">
+      <c r="B26" s="4">
         <v>122</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="5" t="s">
         <v>83</v>
       </c>
       <c r="D26" s="1" t="s">
@@ -1886,15 +1868,15 @@
       <c r="E26" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="5" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="2:7">
-      <c r="B27" s="5">
+      <c r="B27" s="4">
         <v>123</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="5" t="s">
         <v>86</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -1903,314 +1885,278 @@
       <c r="E27" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="2:7">
-      <c r="B28" s="5">
+      <c r="B28" s="4">
         <v>124</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="6">
         <v>-0.5</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="5" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="2:7">
-      <c r="B29" s="5">
+      <c r="B29" s="4">
         <v>125</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="6">
         <v>-0.5</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G29" s="6"/>
+      <c r="G29" s="5"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="2:7">
-      <c r="B30" s="5">
+      <c r="B30" s="4">
         <v>126</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="6">
         <v>-0.5</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="G30" s="6"/>
+      <c r="G30" s="5"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="2:7">
-      <c r="B31" s="5">
+      <c r="B31" s="4">
         <v>127</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E31" s="5">
-        <v>5</v>
-      </c>
-      <c r="F31" s="6" t="s">
+      <c r="E31" s="6">
+        <v>1</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="G31" s="6"/>
+      <c r="G31" s="5"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="2:7">
-      <c r="B32" s="5">
+      <c r="B32" s="4">
         <v>128</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="6">
         <v>1</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="G32" s="6"/>
+      <c r="G32" s="5"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="2:7">
-      <c r="B33" s="5">
+      <c r="B33" s="4">
         <v>129</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="6">
+        <v>100</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G33" s="5"/>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="2:7">
+      <c r="B34" s="4">
+        <v>130</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G34" s="5"/>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="2:7">
+      <c r="B35" s="4">
+        <v>131</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E35" s="6">
+        <v>2</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G35" s="5"/>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="2:7">
+      <c r="B36" s="4">
+        <v>132</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="G36" s="5"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="2:7">
+      <c r="B37" s="4">
+        <v>133</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-2</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G37" s="5"/>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="2:7">
+      <c r="B38" s="4">
+        <v>134</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.5</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G38" s="5"/>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="2:7">
+      <c r="B39" s="4">
+        <v>135</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E39" s="6">
         <v>1</v>
       </c>
-      <c r="F33" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="2:7">
-      <c r="B34" s="5">
+      <c r="F39" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G39" s="5"/>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="2:7">
+      <c r="B40" s="4">
+        <v>136</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="G40" s="5"/>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="2:7">
+      <c r="B41" s="4">
+        <v>137</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E34" s="5">
-        <v>1</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="G34" s="6"/>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="2:7">
-      <c r="B35" s="5">
+      <c r="E41" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E35" s="5">
-        <v>50</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="2:7">
-      <c r="B36" s="5">
+      <c r="G41" s="5"/>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="2:7">
+      <c r="B42" s="4">
+        <v>138</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E36" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G36" s="6"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="2:7">
-      <c r="B37" s="5">
+      <c r="D42" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E37" s="5">
-        <v>2</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="G37" s="6"/>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="2:7">
-      <c r="B38" s="5">
+      <c r="E42" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F42" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E38" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G38" s="6"/>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="2:7">
-      <c r="B39" s="5">
-        <v>135</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E39" s="5">
-        <v>-2</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="G39" s="6"/>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="2:7">
-      <c r="B40" s="5">
-        <v>136</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E40" s="5">
-        <v>-0.5</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G40" s="6"/>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="2:7">
-      <c r="B41" s="5">
-        <v>137</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E41" s="5">
-        <v>1</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="G41" s="6"/>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="2:7">
-      <c r="B42" s="5">
-        <v>138</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G42" s="6"/>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="2:7">
-      <c r="B43" s="5">
-        <v>139</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E43" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="G43" s="6"/>
-    </row>
-    <row r="44" s="1" customFormat="1" spans="2:7">
-      <c r="B44" s="5">
-        <v>140</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E44" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G44" s="6"/>
+      <c r="G42" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/BossEntryConfig.xlsx
+++ b/Config/BossEntryConfig.xlsx
@@ -379,7 +379,7 @@
     <t>ThornShell</t>
   </si>
   <si>
-    <t>本关内玩家每次攻击敌人后,自身会受到该伤害10%的伤害</t>
+    <t>本关内玩家每次攻击敌人后,自身会受到该伤害1%的伤害</t>
   </si>
   <si>
     <t>怨恨之灵</t>
@@ -2043,7 +2043,7 @@
         <v>114</v>
       </c>
       <c r="E36" s="6">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>115</v>

--- a/Config/BossEntryConfig.xlsx
+++ b/Config/BossEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="15045" windowHeight="12240"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1549,7 +1549,7 @@
     <col min="3" max="3" width="8.36666666666667" style="4" customWidth="1"/>
     <col min="4" max="4" width="14.2333333333333" style="3" customWidth="1"/>
     <col min="5" max="5" width="7.39166666666667" style="3" customWidth="1"/>
-    <col min="6" max="6" width="5.325" style="3" customWidth="1"/>
+    <col min="6" max="6" width="9.66666666666667" style="3" customWidth="1"/>
     <col min="7" max="7" width="25.2166666666667" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3" customWidth="1"/>
   </cols>

--- a/Config/BossEntryConfig.xlsx
+++ b/Config/BossEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15045" windowHeight="12240"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -722,12 +722,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1048,7 +1054,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -1072,16 +1078,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -1090,89 +1096,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1182,16 +1188,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1544,90 +1556,91 @@
   <dimension ref="A1:G58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="2.38333333333333" style="3" customWidth="1"/>
-    <col min="2" max="2" width="3.8" style="3" customWidth="1"/>
-    <col min="3" max="3" width="8.36666666666667" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14.2333333333333" style="3" customWidth="1"/>
-    <col min="5" max="5" width="7.39166666666667" style="3" customWidth="1"/>
+    <col min="1" max="1" width="2.38333333333333" style="4" customWidth="1"/>
+    <col min="2" max="2" width="3.8" style="4" customWidth="1"/>
+    <col min="3" max="3" width="8.36666666666667" style="5" customWidth="1"/>
+    <col min="4" max="4" width="14.2333333333333" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7.39166666666667" style="4" customWidth="1"/>
     <col min="6" max="6" width="9.66666666666667" style="3" customWidth="1"/>
-    <col min="7" max="7" width="25.2166666666667" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="3" customWidth="1"/>
+    <col min="7" max="7" width="25.2166666666667" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:7">
-      <c r="C4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:7">
-      <c r="B5" s="7">
+      <c r="B5" s="8">
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1636,10 +1649,10 @@
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -1647,7 +1660,7 @@
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:7">
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1656,10 +1669,10 @@
       <c r="D6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <v>-0.3</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -1667,7 +1680,7 @@
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:7">
-      <c r="B7" s="7">
+      <c r="B7" s="8">
         <v>103</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1676,10 +1689,10 @@
       <c r="D7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <v>1</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
@@ -1687,7 +1700,7 @@
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:7">
-      <c r="B8" s="7">
+      <c r="B8" s="8">
         <v>104</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1696,10 +1709,10 @@
       <c r="D8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <v>0.3</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
@@ -1707,7 +1720,7 @@
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:7">
-      <c r="B9" s="7">
+      <c r="B9" s="8">
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1719,7 +1732,7 @@
       <c r="E9" s="1">
         <v>0.25</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
@@ -1727,7 +1740,7 @@
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:7">
-      <c r="B10" s="7">
+      <c r="B10" s="8">
         <v>106</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1739,7 +1752,7 @@
       <c r="E10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
@@ -1747,7 +1760,7 @@
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:7">
-      <c r="B11" s="7">
+      <c r="B11" s="8">
         <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1759,7 +1772,7 @@
       <c r="E11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
@@ -1767,7 +1780,7 @@
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:7">
-      <c r="B12" s="7">
+      <c r="B12" s="8">
         <v>108</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1779,7 +1792,7 @@
       <c r="E12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
@@ -1787,7 +1800,7 @@
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:7">
-      <c r="B13" s="7">
+      <c r="B13" s="8">
         <v>109</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1796,10 +1809,10 @@
       <c r="D13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="8">
         <v>4</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
@@ -1807,7 +1820,7 @@
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:7">
-      <c r="B14" s="7">
+      <c r="B14" s="8">
         <v>110</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1816,10 +1829,10 @@
       <c r="D14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="6">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
@@ -1827,7 +1840,7 @@
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:7">
-      <c r="B15" s="7">
+      <c r="B15" s="8">
         <v>111</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1836,10 +1849,10 @@
       <c r="D15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="8">
         <v>1</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="6">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
@@ -1847,7 +1860,7 @@
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:7">
-      <c r="B16" s="7">
+      <c r="B16" s="8">
         <v>112</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1856,10 +1869,10 @@
       <c r="D16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="8">
         <v>7</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="6">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
@@ -1867,7 +1880,7 @@
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="2:7">
-      <c r="B17" s="7">
+      <c r="B17" s="8">
         <v>113</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -1876,10 +1889,10 @@
       <c r="D17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="8">
         <v>0.05</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="6">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
@@ -1887,7 +1900,7 @@
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="2:7">
-      <c r="B18" s="7">
+      <c r="B18" s="8">
         <v>114</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1896,10 +1909,10 @@
       <c r="D18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="8">
         <v>1</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="6">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
@@ -1907,7 +1920,7 @@
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="2:7">
-      <c r="B19" s="7">
+      <c r="B19" s="8">
         <v>115</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1916,10 +1929,10 @@
       <c r="D19" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="8">
         <v>1</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="6">
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
@@ -1927,7 +1940,7 @@
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="2:7">
-      <c r="B20" s="7">
+      <c r="B20" s="8">
         <v>116</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1936,10 +1949,10 @@
       <c r="D20" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="8">
         <v>1</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="6">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
@@ -1947,7 +1960,7 @@
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="2:7">
-      <c r="B21" s="7">
+      <c r="B21" s="8">
         <v>117</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1956,10 +1969,10 @@
       <c r="D21" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="8">
         <v>1</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="6">
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
@@ -1967,7 +1980,7 @@
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="2:7">
-      <c r="B22" s="7">
+      <c r="B22" s="8">
         <v>118</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1976,10 +1989,10 @@
       <c r="D22" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="8">
         <v>1</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="6">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
@@ -1987,7 +2000,7 @@
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="2:7">
-      <c r="B23" s="7">
+      <c r="B23" s="8">
         <v>119</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -1996,10 +2009,10 @@
       <c r="D23" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="8">
         <v>1</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="6">
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
@@ -2007,7 +2020,7 @@
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="2:7">
-      <c r="B24" s="7">
+      <c r="B24" s="8">
         <v>120</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -2019,7 +2032,7 @@
       <c r="E24" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="6">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
@@ -2027,7 +2040,7 @@
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="2:7">
-      <c r="B25" s="7">
+      <c r="B25" s="8">
         <v>121</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -2039,7 +2052,7 @@
       <c r="E25" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="6">
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
@@ -2047,7 +2060,7 @@
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="2:7">
-      <c r="B26" s="7">
+      <c r="B26" s="8">
         <v>122</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -2059,7 +2072,7 @@
       <c r="E26" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="6">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
@@ -2067,7 +2080,7 @@
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="2:7">
-      <c r="B27" s="7">
+      <c r="B27" s="8">
         <v>123</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -2079,7 +2092,7 @@
       <c r="E27" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="6">
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
@@ -2087,7 +2100,7 @@
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="2:7">
-      <c r="B28" s="7">
+      <c r="B28" s="8">
         <v>124</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -2096,10 +2109,10 @@
       <c r="D28" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="8">
         <v>-0.5</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="6">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
@@ -2107,7 +2120,7 @@
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="2:7">
-      <c r="B29" s="7">
+      <c r="B29" s="8">
         <v>125</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -2116,10 +2129,10 @@
       <c r="D29" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="8">
         <v>-0.5</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="6">
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
@@ -2127,7 +2140,7 @@
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="2:7">
-      <c r="B30" s="7">
+      <c r="B30" s="8">
         <v>126</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -2136,10 +2149,10 @@
       <c r="D30" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="8">
         <v>-0.5</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="6">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
@@ -2147,7 +2160,7 @@
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="2:7">
-      <c r="B31" s="7">
+      <c r="B31" s="8">
         <v>127</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -2156,10 +2169,10 @@
       <c r="D31" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="8">
         <v>1</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="6">
         <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
@@ -2167,7 +2180,7 @@
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="2:7">
-      <c r="B32" s="7">
+      <c r="B32" s="8">
         <v>128</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -2176,10 +2189,10 @@
       <c r="D32" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="8">
         <v>1</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="6">
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
@@ -2187,7 +2200,7 @@
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="2:7">
-      <c r="B33" s="7">
+      <c r="B33" s="8">
         <v>129</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -2196,10 +2209,10 @@
       <c r="D33" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="8">
         <v>100</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="6">
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
@@ -2207,7 +2220,7 @@
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="2:7">
-      <c r="B34" s="7">
+      <c r="B34" s="8">
         <v>130</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -2216,10 +2229,10 @@
       <c r="D34" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="8">
         <v>0.1</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="6">
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
@@ -2227,7 +2240,7 @@
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="2:7">
-      <c r="B35" s="7">
+      <c r="B35" s="8">
         <v>131</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -2236,10 +2249,10 @@
       <c r="D35" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="8">
         <v>2</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="6">
         <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
@@ -2247,7 +2260,7 @@
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="2:7">
-      <c r="B36" s="7">
+      <c r="B36" s="8">
         <v>132</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -2256,10 +2269,10 @@
       <c r="D36" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="8">
         <v>0.01</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="6">
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
@@ -2267,7 +2280,7 @@
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="2:7">
-      <c r="B37" s="7">
+      <c r="B37" s="8">
         <v>133</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -2276,10 +2289,10 @@
       <c r="D37" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="8">
         <v>-2</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37" s="6">
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
@@ -2287,7 +2300,7 @@
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="2:7">
-      <c r="B38" s="7">
+      <c r="B38" s="8">
         <v>134</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -2296,10 +2309,10 @@
       <c r="D38" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="8">
         <v>-0.5</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="6">
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
@@ -2307,7 +2320,7 @@
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="2:7">
-      <c r="B39" s="7">
+      <c r="B39" s="8">
         <v>135</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -2316,10 +2329,10 @@
       <c r="D39" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="8">
         <v>1</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="6">
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
@@ -2327,7 +2340,7 @@
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="2:7">
-      <c r="B40" s="7">
+      <c r="B40" s="8">
         <v>136</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -2336,10 +2349,10 @@
       <c r="D40" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="6">
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
@@ -2347,7 +2360,7 @@
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="2:7">
-      <c r="B41" s="7">
+      <c r="B41" s="8">
         <v>137</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -2356,10 +2369,10 @@
       <c r="D41" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="8">
         <v>0.2</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="6">
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
@@ -2367,7 +2380,7 @@
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="2:7">
-      <c r="B42" s="7">
+      <c r="B42" s="8">
         <v>138</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -2376,10 +2389,10 @@
       <c r="D42" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E42" s="8">
         <v>0.25</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="6">
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
@@ -2387,222 +2400,227 @@
       </c>
     </row>
     <row r="43" s="2" customFormat="1" spans="2:7">
-      <c r="B43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-    </row>
-    <row r="44" s="1" customFormat="1" spans="2:7">
-      <c r="B44" s="7">
+      <c r="B43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" s="3" customFormat="1" spans="2:7">
+      <c r="B44" s="6">
         <v>201</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E44" s="6">
         <v>1</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="6">
         <v>1</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="9" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" spans="2:7">
-      <c r="B45" s="7">
+    <row r="45" s="3" customFormat="1" spans="2:7">
+      <c r="B45" s="6">
         <v>202</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="6">
         <v>1</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="9" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" spans="2:7">
-      <c r="B46" s="7">
+    <row r="46" s="3" customFormat="1" spans="2:7">
+      <c r="B46" s="6">
         <v>203</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F46" s="6">
         <v>1</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" s="9" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" spans="2:7">
-      <c r="B47" s="7">
+    <row r="47" s="3" customFormat="1" spans="2:7">
+      <c r="B47" s="6">
         <v>204</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F47" s="6">
         <v>1</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G47" s="9" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1" spans="2:7">
-      <c r="B48" s="7">
+    <row r="48" s="3" customFormat="1" spans="2:7">
+      <c r="B48" s="6">
         <v>205</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F48" s="6">
         <v>1</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G48" s="9" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" spans="2:7">
-      <c r="B49" s="7">
+    <row r="49" s="3" customFormat="1" spans="2:7">
+      <c r="B49" s="6">
         <v>206</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F49" s="6">
         <v>1</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G49" s="9" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" spans="2:7">
-      <c r="B50" s="7">
+    <row r="50" s="3" customFormat="1" spans="2:7">
+      <c r="B50" s="6">
         <v>207</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F50" s="6">
         <v>1</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="G50" s="9" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" spans="2:7">
-      <c r="B51" s="7">
+    <row r="51" s="3" customFormat="1" spans="2:7">
+      <c r="B51" s="6">
         <v>208</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F51" s="6">
         <v>1</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G51" s="9" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" spans="2:7">
-      <c r="B52" s="7">
+    <row r="52" s="3" customFormat="1" spans="2:7">
+      <c r="B52" s="6">
         <v>209</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="E52" s="7" t="s">
+      <c r="E52" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F52" s="6">
         <v>1</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" s="9" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" spans="2:7">
-      <c r="B53" s="7">
+    <row r="53" s="3" customFormat="1" spans="2:7">
+      <c r="B53" s="6">
         <v>210</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7">
+      <c r="E53" s="6"/>
+      <c r="F53" s="6">
         <v>1</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" s="9" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="2:7">
-      <c r="C54" s="6"/>
+      <c r="C54" s="7"/>
+      <c r="F54" s="3"/>
     </row>
     <row r="55" s="1" customFormat="1" spans="2:7">
-      <c r="C55" s="6"/>
+      <c r="C55" s="7"/>
+      <c r="F55" s="3"/>
     </row>
     <row r="56" s="1" customFormat="1" spans="2:7">
-      <c r="C56" s="6"/>
+      <c r="C56" s="7"/>
+      <c r="F56" s="3"/>
     </row>
     <row r="57" s="1" customFormat="1" spans="2:7">
-      <c r="C57" s="6"/>
+      <c r="C57" s="7"/>
+      <c r="F57" s="3"/>
     </row>
     <row r="58" s="1" customFormat="1" spans="2:7">
-      <c r="C58" s="6"/>
+      <c r="C58" s="7"/>
+      <c r="F58" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/BossEntryConfig.xlsx
+++ b/Config/BossEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="13920" windowHeight="10245"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1178,7 +1178,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1195,11 +1195,17 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1561,7 +1567,7 @@
     <col min="3" max="3" width="8.36666666666667" style="5" customWidth="1"/>
     <col min="4" max="4" width="14.2333333333333" style="4" customWidth="1"/>
     <col min="5" max="5" width="7.39166666666667" style="4" customWidth="1"/>
-    <col min="6" max="6" width="9.66666666666667" style="3" customWidth="1"/>
+    <col min="6" max="6" width="9.66666666666667" style="6" customWidth="1"/>
     <col min="7" max="7" width="25.2166666666667" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4" customWidth="1"/>
   </cols>
@@ -1582,7 +1588,7 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
@@ -1605,7 +1611,7 @@
       <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G2" s="4" t="s">
@@ -1628,7 +1634,7 @@
       <c r="E3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="4" t="s">
@@ -1636,11 +1642,11 @@
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:7">
-      <c r="C4" s="7"/>
-      <c r="F4" s="3"/>
+      <c r="C4" s="8"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:7">
-      <c r="B5" s="8">
+      <c r="B5" s="9">
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1649,10 +1655,10 @@
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -1660,7 +1666,7 @@
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:7">
-      <c r="B6" s="8">
+      <c r="B6" s="9">
         <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1669,10 +1675,10 @@
       <c r="D6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="9">
         <v>-0.3</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -1680,7 +1686,7 @@
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:7">
-      <c r="B7" s="8">
+      <c r="B7" s="9">
         <v>103</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1689,10 +1695,10 @@
       <c r="D7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="9">
         <v>1</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
@@ -1700,7 +1706,7 @@
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:7">
-      <c r="B8" s="8">
+      <c r="B8" s="9">
         <v>104</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1709,10 +1715,10 @@
       <c r="D8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="9">
         <v>0.3</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
@@ -1720,7 +1726,7 @@
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:7">
-      <c r="B9" s="8">
+      <c r="B9" s="9">
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1732,7 +1738,7 @@
       <c r="E9" s="1">
         <v>0.25</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
@@ -1740,7 +1746,7 @@
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:7">
-      <c r="B10" s="8">
+      <c r="B10" s="9">
         <v>106</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1752,7 +1758,7 @@
       <c r="E10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
@@ -1760,7 +1766,7 @@
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:7">
-      <c r="B11" s="8">
+      <c r="B11" s="9">
         <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1772,7 +1778,7 @@
       <c r="E11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
@@ -1780,7 +1786,7 @@
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:7">
-      <c r="B12" s="8">
+      <c r="B12" s="9">
         <v>108</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1792,7 +1798,7 @@
       <c r="E12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="7">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
@@ -1800,7 +1806,7 @@
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:7">
-      <c r="B13" s="8">
+      <c r="B13" s="9">
         <v>109</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1809,10 +1815,10 @@
       <c r="D13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="9">
         <v>4</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="7">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
@@ -1820,7 +1826,7 @@
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:7">
-      <c r="B14" s="8">
+      <c r="B14" s="9">
         <v>110</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1829,10 +1835,10 @@
       <c r="D14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="7">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
@@ -1840,7 +1846,7 @@
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:7">
-      <c r="B15" s="8">
+      <c r="B15" s="9">
         <v>111</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1849,10 +1855,10 @@
       <c r="D15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="9">
         <v>1</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="7">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
@@ -1860,7 +1866,7 @@
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:7">
-      <c r="B16" s="8">
+      <c r="B16" s="9">
         <v>112</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1869,10 +1875,10 @@
       <c r="D16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="9">
         <v>7</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="7">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
@@ -1880,7 +1886,7 @@
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="2:7">
-      <c r="B17" s="8">
+      <c r="B17" s="9">
         <v>113</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -1889,10 +1895,10 @@
       <c r="D17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="9">
         <v>0.05</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="7">
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
@@ -1900,7 +1906,7 @@
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="2:7">
-      <c r="B18" s="8">
+      <c r="B18" s="9">
         <v>114</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1909,10 +1915,10 @@
       <c r="D18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="9">
         <v>1</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="7">
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
@@ -1920,7 +1926,7 @@
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="2:7">
-      <c r="B19" s="8">
+      <c r="B19" s="9">
         <v>115</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1929,10 +1935,10 @@
       <c r="D19" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="9">
         <v>1</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="7">
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
@@ -1940,7 +1946,7 @@
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="2:7">
-      <c r="B20" s="8">
+      <c r="B20" s="9">
         <v>116</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1949,10 +1955,10 @@
       <c r="D20" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="9">
         <v>1</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="7">
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
@@ -1960,7 +1966,7 @@
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="2:7">
-      <c r="B21" s="8">
+      <c r="B21" s="9">
         <v>117</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1969,10 +1975,10 @@
       <c r="D21" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="9">
         <v>1</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="7">
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
@@ -1980,7 +1986,7 @@
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="2:7">
-      <c r="B22" s="8">
+      <c r="B22" s="9">
         <v>118</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1989,10 +1995,10 @@
       <c r="D22" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="9">
         <v>1</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="7">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
@@ -2000,7 +2006,7 @@
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="2:7">
-      <c r="B23" s="8">
+      <c r="B23" s="9">
         <v>119</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -2009,10 +2015,10 @@
       <c r="D23" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="9">
         <v>1</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="7">
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
@@ -2020,7 +2026,7 @@
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="2:7">
-      <c r="B24" s="8">
+      <c r="B24" s="9">
         <v>120</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -2032,7 +2038,7 @@
       <c r="E24" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="7">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
@@ -2040,7 +2046,7 @@
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="2:7">
-      <c r="B25" s="8">
+      <c r="B25" s="9">
         <v>121</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -2052,7 +2058,7 @@
       <c r="E25" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="7">
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
@@ -2060,7 +2066,7 @@
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="2:7">
-      <c r="B26" s="8">
+      <c r="B26" s="9">
         <v>122</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -2072,7 +2078,7 @@
       <c r="E26" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="7">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
@@ -2080,7 +2086,7 @@
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="2:7">
-      <c r="B27" s="8">
+      <c r="B27" s="9">
         <v>123</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -2092,7 +2098,7 @@
       <c r="E27" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="7">
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
@@ -2100,7 +2106,7 @@
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="2:7">
-      <c r="B28" s="8">
+      <c r="B28" s="9">
         <v>124</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -2109,10 +2115,10 @@
       <c r="D28" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="9">
         <v>-0.5</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="7">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
@@ -2120,7 +2126,7 @@
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="2:7">
-      <c r="B29" s="8">
+      <c r="B29" s="9">
         <v>125</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -2129,10 +2135,10 @@
       <c r="D29" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="9">
         <v>-0.5</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="7">
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
@@ -2140,7 +2146,7 @@
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="2:7">
-      <c r="B30" s="8">
+      <c r="B30" s="9">
         <v>126</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -2149,10 +2155,10 @@
       <c r="D30" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="9">
         <v>-0.5</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="7">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
@@ -2160,7 +2166,7 @@
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="2:7">
-      <c r="B31" s="8">
+      <c r="B31" s="9">
         <v>127</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -2169,10 +2175,10 @@
       <c r="D31" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="9">
         <v>1</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="7">
         <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
@@ -2180,7 +2186,7 @@
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="2:7">
-      <c r="B32" s="8">
+      <c r="B32" s="9">
         <v>128</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -2189,10 +2195,10 @@
       <c r="D32" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="9">
         <v>1</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="7">
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
@@ -2200,7 +2206,7 @@
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="2:7">
-      <c r="B33" s="8">
+      <c r="B33" s="9">
         <v>129</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -2209,10 +2215,10 @@
       <c r="D33" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="9">
         <v>100</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="7">
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
@@ -2220,7 +2226,7 @@
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="2:7">
-      <c r="B34" s="8">
+      <c r="B34" s="9">
         <v>130</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -2229,10 +2235,10 @@
       <c r="D34" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="9">
         <v>0.1</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="7">
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
@@ -2240,7 +2246,7 @@
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="2:7">
-      <c r="B35" s="8">
+      <c r="B35" s="9">
         <v>131</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -2249,10 +2255,10 @@
       <c r="D35" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="9">
         <v>2</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="7">
         <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
@@ -2260,7 +2266,7 @@
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="2:7">
-      <c r="B36" s="8">
+      <c r="B36" s="9">
         <v>132</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -2269,10 +2275,10 @@
       <c r="D36" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E36" s="9">
         <v>0.01</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="7">
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
@@ -2280,7 +2286,7 @@
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="2:7">
-      <c r="B37" s="8">
+      <c r="B37" s="9">
         <v>133</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -2289,10 +2295,10 @@
       <c r="D37" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E37" s="8">
+      <c r="E37" s="9">
         <v>-2</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37" s="7">
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
@@ -2300,7 +2306,7 @@
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="2:7">
-      <c r="B38" s="8">
+      <c r="B38" s="9">
         <v>134</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -2309,10 +2315,10 @@
       <c r="D38" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E38" s="8">
+      <c r="E38" s="9">
         <v>-0.5</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="7">
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
@@ -2320,7 +2326,7 @@
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="2:7">
-      <c r="B39" s="8">
+      <c r="B39" s="9">
         <v>135</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -2329,10 +2335,10 @@
       <c r="D39" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="9">
         <v>1</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F39" s="7">
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
@@ -2340,7 +2346,7 @@
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="2:7">
-      <c r="B40" s="8">
+      <c r="B40" s="9">
         <v>136</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -2349,10 +2355,10 @@
       <c r="D40" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F40" s="7">
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
@@ -2360,7 +2366,7 @@
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="2:7">
-      <c r="B41" s="8">
+      <c r="B41" s="9">
         <v>137</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -2369,10 +2375,10 @@
       <c r="D41" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E41" s="8">
+      <c r="E41" s="9">
         <v>0.2</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F41" s="7">
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
@@ -2380,7 +2386,7 @@
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="2:7">
-      <c r="B42" s="8">
+      <c r="B42" s="9">
         <v>138</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -2389,10 +2395,10 @@
       <c r="D42" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E42" s="8">
+      <c r="E42" s="9">
         <v>0.25</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F42" s="7">
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
@@ -2400,227 +2406,227 @@
       </c>
     </row>
     <row r="43" s="2" customFormat="1" spans="2:7">
-      <c r="B43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="6"/>
+      <c r="B43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="7"/>
     </row>
     <row r="44" s="3" customFormat="1" spans="2:7">
-      <c r="B44" s="6">
+      <c r="B44" s="10">
         <v>201</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E44" s="10">
         <v>1</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F44" s="7">
         <v>1</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="11" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="45" s="3" customFormat="1" spans="2:7">
-      <c r="B45" s="6">
+      <c r="B45" s="10">
         <v>202</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F45" s="6">
+      <c r="F45" s="7">
         <v>1</v>
       </c>
-      <c r="G45" s="9" t="s">
+      <c r="G45" s="11" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" spans="2:7">
-      <c r="B46" s="6">
+      <c r="B46" s="10">
         <v>203</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="F46" s="6">
+      <c r="F46" s="7">
         <v>1</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="11" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" spans="2:7">
-      <c r="B47" s="6">
+      <c r="B47" s="10">
         <v>204</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="F47" s="6">
+      <c r="F47" s="7">
         <v>1</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G47" s="11" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" spans="2:7">
-      <c r="B48" s="6">
+      <c r="B48" s="10">
         <v>205</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C48" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="D48" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F48" s="7">
         <v>1</v>
       </c>
-      <c r="G48" s="9" t="s">
+      <c r="G48" s="11" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="49" s="3" customFormat="1" spans="2:7">
-      <c r="B49" s="6">
+      <c r="B49" s="10">
         <v>206</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E49" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="F49" s="6">
+      <c r="F49" s="7">
         <v>1</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="G49" s="11" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="50" s="3" customFormat="1" spans="2:7">
-      <c r="B50" s="6">
+      <c r="B50" s="10">
         <v>207</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C50" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D50" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F50" s="7">
         <v>1</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="G50" s="11" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="51" s="3" customFormat="1" spans="2:7">
-      <c r="B51" s="6">
+      <c r="B51" s="10">
         <v>208</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C51" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="D51" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E51" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F51" s="7">
         <v>1</v>
       </c>
-      <c r="G51" s="9" t="s">
+      <c r="G51" s="11" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="52" s="3" customFormat="1" spans="2:7">
-      <c r="B52" s="6">
+      <c r="B52" s="10">
         <v>209</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52" s="7">
         <v>1</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="G52" s="11" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" spans="2:7">
-      <c r="B53" s="6">
+      <c r="B53" s="10">
         <v>210</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C53" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="D53" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6">
+      <c r="E53" s="10"/>
+      <c r="F53" s="7">
         <v>1</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="G53" s="11" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="2:7">
-      <c r="C54" s="7"/>
-      <c r="F54" s="3"/>
+      <c r="C54" s="8"/>
+      <c r="F54" s="6"/>
     </row>
     <row r="55" s="1" customFormat="1" spans="2:7">
-      <c r="C55" s="7"/>
-      <c r="F55" s="3"/>
+      <c r="C55" s="8"/>
+      <c r="F55" s="6"/>
     </row>
     <row r="56" s="1" customFormat="1" spans="2:7">
-      <c r="C56" s="7"/>
-      <c r="F56" s="3"/>
+      <c r="C56" s="8"/>
+      <c r="F56" s="6"/>
     </row>
     <row r="57" s="1" customFormat="1" spans="2:7">
-      <c r="C57" s="7"/>
-      <c r="F57" s="3"/>
+      <c r="C57" s="8"/>
+      <c r="F57" s="6"/>
     </row>
     <row r="58" s="1" customFormat="1" spans="2:7">
-      <c r="C58" s="7"/>
-      <c r="F58" s="3"/>
+      <c r="C58" s="8"/>
+      <c r="F58" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
